--- a/equipment_tables.xlsx
+++ b/equipment_tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pantonmcleod-my.sharepoint.com/personal/alex_campbell_pantonmcleod_co_uk/Documents/CodeStuffs/equipment_portal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{65FC2E82-7604-41E0-B33D-F59F96D9306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B4C0DF4-5FF2-405D-9DE2-88390D319AA7}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{65FC2E82-7604-41E0-B33D-F59F96D9306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{162CA050-1AF2-4D2D-A3C9-0C9433AF6953}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3B0124D6-ED40-4854-9E06-1CC63E7C882D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{3B0124D6-ED40-4854-9E06-1CC63E7C882D}"/>
   </bookViews>
   <sheets>
     <sheet name="GEN" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="249">
   <si>
     <t>SAGE REFERENCE</t>
   </si>
@@ -268,9 +268,6 @@
     <t>Wales</t>
   </si>
   <si>
-    <t xml:space="preserve">All Wales Pumps and Gennys have been altered to 12 months </t>
-  </si>
-  <si>
     <t>GEN029</t>
   </si>
   <si>
@@ -286,9 +283,6 @@
     <t>GCBCH-1362433 (14644)</t>
   </si>
   <si>
-    <t>QR made</t>
-  </si>
-  <si>
     <t>GEN035</t>
   </si>
   <si>
@@ -319,18 +313,12 @@
     <t>GCBCT-3906396 (803951)</t>
   </si>
   <si>
-    <t>SW69 CHF</t>
-  </si>
-  <si>
     <t>GEN038</t>
   </si>
   <si>
     <t>GCBCT-4077443 (801336)</t>
   </si>
   <si>
-    <t xml:space="preserve">idk where </t>
-  </si>
-  <si>
     <t>GEN037</t>
   </si>
   <si>
@@ -364,9 +352,6 @@
     <t xml:space="preserve">GCBGT-2670588 (802494) </t>
   </si>
   <si>
-    <t>repairs??</t>
-  </si>
-  <si>
     <t>GEN044</t>
   </si>
   <si>
@@ -406,9 +391,6 @@
     <t>GCBDH-1121696 (11686)</t>
   </si>
   <si>
-    <t>ireland</t>
-  </si>
-  <si>
     <t>GEN041</t>
   </si>
   <si>
@@ -466,9 +448,6 @@
     <t>GCBCH-1195750 (210601013)</t>
   </si>
   <si>
-    <t>in GW corner??</t>
-  </si>
-  <si>
     <t>PUM028</t>
   </si>
   <si>
@@ -505,9 +484,6 @@
     <t>GCBCH-1458268 (230701048)</t>
   </si>
   <si>
-    <t xml:space="preserve">in pile </t>
-  </si>
-  <si>
     <t>PUM001</t>
   </si>
   <si>
@@ -520,9 +496,6 @@
     <t>GCBPT-2261693 (160801026)</t>
   </si>
   <si>
-    <t>wouldn’t start</t>
-  </si>
-  <si>
     <t>PUM002</t>
   </si>
   <si>
@@ -535,9 +508,6 @@
     <t>GCBPT-2262015 (160801030)</t>
   </si>
   <si>
-    <t>Might need replacement frame later</t>
-  </si>
-  <si>
     <t>PUM022</t>
   </si>
   <si>
@@ -601,9 +571,6 @@
     <t>G200F-T8300020100071027</t>
   </si>
   <si>
-    <t>have I seen?</t>
-  </si>
-  <si>
     <t>G200F-T8300020100071033</t>
   </si>
   <si>
@@ -628,9 +595,6 @@
     <t>R210-A1803005638</t>
   </si>
   <si>
-    <t xml:space="preserve">ireland </t>
-  </si>
-  <si>
     <t>R210-A1803005648</t>
   </si>
   <si>
@@ -667,36 +631,24 @@
     <t>SUB008</t>
   </si>
   <si>
-    <t>4 2" RS550 (small) in selkirk</t>
-  </si>
-  <si>
     <t>SUB014</t>
   </si>
   <si>
     <t>?</t>
   </si>
   <si>
-    <t>2 2" RS750 (big) selkirk 1 in GW corner</t>
-  </si>
-  <si>
     <t>SUB015</t>
   </si>
   <si>
     <t>SOR274132/SDN288246</t>
   </si>
   <si>
-    <t>1 more 2" in cza</t>
-  </si>
-  <si>
     <t>SUB019</t>
   </si>
   <si>
     <t>187951</t>
   </si>
   <si>
-    <t>1 more 2" in byg (87699)</t>
-  </si>
-  <si>
     <t>SUB020</t>
   </si>
   <si>
@@ -712,9 +664,6 @@
     <t>ESF116685</t>
   </si>
   <si>
-    <t>1 in GW corner</t>
-  </si>
-  <si>
     <t>SUB022</t>
   </si>
   <si>
@@ -724,9 +673,6 @@
     <t>SUB023</t>
   </si>
   <si>
-    <t>2 2" in OFU</t>
-  </si>
-  <si>
     <t>SUB024</t>
   </si>
   <si>
@@ -787,9 +733,6 @@
     <t>ESF127240</t>
   </si>
   <si>
-    <t xml:space="preserve">hugh has some </t>
-  </si>
-  <si>
     <t>SUB041</t>
   </si>
   <si>
@@ -823,25 +766,163 @@
     <t>PUM108</t>
   </si>
   <si>
-    <t>2" Submersible</t>
-  </si>
-  <si>
-    <t>4" Submersible</t>
-  </si>
-  <si>
-    <t>3" Submersible</t>
-  </si>
-  <si>
-    <t>BETA Dosing Pump</t>
-  </si>
-  <si>
-    <t>replaced</t>
-  </si>
-  <si>
-    <t>SIGMA Dosing Pump</t>
-  </si>
-  <si>
     <t>chemical pumps are fucked</t>
+  </si>
+  <si>
+    <t>old</t>
+  </si>
+  <si>
+    <t>SL26 BZJ</t>
+  </si>
+  <si>
+    <t>------&gt;</t>
+  </si>
+  <si>
+    <t>joe repairs</t>
+  </si>
+  <si>
+    <t>in BFO</t>
+  </si>
+  <si>
+    <t>BZJ</t>
+  </si>
+  <si>
+    <t>SL26 BCO</t>
+  </si>
+  <si>
+    <t>repairs?? Never seen</t>
+  </si>
+  <si>
+    <t>JUST FOUND OUT ABT</t>
+  </si>
+  <si>
+    <t>G200F-07030306083</t>
+  </si>
+  <si>
+    <t>GEN049</t>
+  </si>
+  <si>
+    <t>16447 (GCBDH-1228650)</t>
+  </si>
+  <si>
+    <t>new one davie had last</t>
+  </si>
+  <si>
+    <t>SL26 BFO</t>
+  </si>
+  <si>
+    <t>wales maybe</t>
+  </si>
+  <si>
+    <t>Service overdue</t>
+  </si>
+  <si>
+    <t>N/a</t>
+  </si>
+  <si>
+    <t>In Service</t>
+  </si>
+  <si>
+    <t>Set for service</t>
+  </si>
+  <si>
+    <t>SL26 CXF</t>
+  </si>
+  <si>
+    <t>needs qr</t>
+  </si>
+  <si>
+    <t>PUM044</t>
+  </si>
+  <si>
+    <t>GCBCH-1600521 (240401018)</t>
+  </si>
+  <si>
+    <t>PUM045</t>
+  </si>
+  <si>
+    <t>villers</t>
+  </si>
+  <si>
+    <t>R210-A2304141436</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>New pump needs made up</t>
+  </si>
+  <si>
+    <t>fucked</t>
+  </si>
+  <si>
+    <t>2"</t>
+  </si>
+  <si>
+    <t>ESF127024 3" written-off?</t>
+  </si>
+  <si>
+    <t>4"</t>
+  </si>
+  <si>
+    <t>237349 2" @repairs</t>
+  </si>
+  <si>
+    <t>xxx0967 @repairs</t>
+  </si>
+  <si>
+    <t>2x 2" @repairs</t>
+  </si>
+  <si>
+    <t>3"</t>
+  </si>
+  <si>
+    <t>1x 3" @submersible cub</t>
+  </si>
+  <si>
+    <t>2x 2" @submersible cub</t>
+  </si>
+  <si>
+    <t>needs repairs</t>
+  </si>
+  <si>
+    <t>idk</t>
+  </si>
+  <si>
+    <t>SUB043</t>
+  </si>
+  <si>
+    <t>WEDA 230V</t>
+  </si>
+  <si>
+    <t>SUB044</t>
+  </si>
+  <si>
+    <t>SUB045</t>
+  </si>
+  <si>
+    <t>PUM102</t>
+  </si>
+  <si>
+    <t>SOLENOID W/FOOTBRACKET</t>
+  </si>
+  <si>
+    <t>Selkirk?</t>
+  </si>
+  <si>
+    <t>Possibly 240V (no S/N)</t>
+  </si>
+  <si>
+    <t>selkirk</t>
+  </si>
+  <si>
+    <t>PUM112</t>
+  </si>
+  <si>
+    <t>SIGMA</t>
+  </si>
+  <si>
+    <t>stolen</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1260,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1339,9 +1420,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1360,22 +1438,46 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1383,7 +1485,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{84664C61-458C-465E-9F74-3D1CD7A96CE6}"/>
   </cellStyles>
-  <dxfs count="86">
+  <dxfs count="155">
     <dxf>
       <fill>
         <patternFill>
@@ -1402,233 +1504,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1905,7 +1780,67 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2096,6 +2031,334 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2121,226 +2384,203 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
         <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2543,6 +2783,399 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2605,99 +3238,95 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E841238-B8AA-42F8-980F-A0F39CF45CE4}" name="Generators" displayName="Generators" ref="A1:L28" totalsRowShown="0" headerRowDxfId="85" dataDxfId="84">
-  <autoFilter ref="A1:L28" xr:uid="{4E841238-B8AA-42F8-980F-A0F39CF45CE4}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L28">
-    <sortCondition ref="A1:A28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E841238-B8AA-42F8-980F-A0F39CF45CE4}" name="Generators" displayName="Generators" ref="A1:L30" totalsRowShown="0" headerRowDxfId="105" dataDxfId="104">
+  <autoFilter ref="A1:L30" xr:uid="{4E841238-B8AA-42F8-980F-A0F39CF45CE4}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L30">
+    <sortCondition ref="A1:A30"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{FBF01029-8468-45F8-8289-F1508C6D786C}" name="SAGE REFERENCE" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{EC225BC8-04F4-4324-B0DE-B4CD46E03F66}" name="Equipment type " dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{37107A79-CB14-4F32-9AF9-46348026DEEC}" name="Model " dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{FBF01029-8468-45F8-8289-F1508C6D786C}" name="SAGE REFERENCE" dataDxfId="103"/>
+    <tableColumn id="2" xr3:uid="{EC225BC8-04F4-4324-B0DE-B4CD46E03F66}" name="Equipment type " dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{37107A79-CB14-4F32-9AF9-46348026DEEC}" name="Model " dataDxfId="101"/>
     <tableColumn id="4" xr3:uid="{74379293-C2C2-40ED-A7CE-6BC0F776D9A0}" name="Serial Number"/>
-    <tableColumn id="5" xr3:uid="{E4D44111-B1DF-484F-9884-E96DC694E68B}" name="Date into Service" dataDxfId="80"/>
-    <tableColumn id="6" xr3:uid="{BDAFA9A1-B7D9-4D3F-B9F2-37BCAE981C7F}" name="Last Service" dataDxfId="79"/>
-    <tableColumn id="7" xr3:uid="{4B95D808-A111-42A5-93AB-44AA25A09A8E}" name="Next Service" dataDxfId="78"/>
-    <tableColumn id="8" xr3:uid="{0EAA17DF-9A0C-43F3-A5A7-AE7960F67890}" name="Service status" dataDxfId="77">
-      <calculatedColumnFormula>IF(G2&lt;TODAY(),"Service overdue","In Service")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{E758CE80-AE90-4337-8979-209D9A5D3CF5}" name="Days to next service" dataDxfId="76">
-      <calculatedColumnFormula>IF((G2-TODAY())&gt;0,(G2-TODAY()),"N/a")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{5F6881B6-5E1F-4282-A48D-BDABFEE16414}" name="Location" dataDxfId="75"/>
-    <tableColumn id="11" xr3:uid="{90463963-07D5-41E4-BF61-BFD7B42D2A8F}" name="Notes" dataDxfId="74"/>
-    <tableColumn id="12" xr3:uid="{C591FF9E-CAEC-4B9E-9E09-27AF2E069563}" name="QR Applied" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{E4D44111-B1DF-484F-9884-E96DC694E68B}" name="Date into Service" dataDxfId="100"/>
+    <tableColumn id="6" xr3:uid="{BDAFA9A1-B7D9-4D3F-B9F2-37BCAE981C7F}" name="Last Service" dataDxfId="99"/>
+    <tableColumn id="7" xr3:uid="{4B95D808-A111-42A5-93AB-44AA25A09A8E}" name="Next Service" dataDxfId="98"/>
+    <tableColumn id="8" xr3:uid="{0EAA17DF-9A0C-43F3-A5A7-AE7960F67890}" name="Service status" dataDxfId="97"/>
+    <tableColumn id="9" xr3:uid="{E758CE80-AE90-4337-8979-209D9A5D3CF5}" name="Days to next service" dataDxfId="96"/>
+    <tableColumn id="10" xr3:uid="{5F6881B6-5E1F-4282-A48D-BDABFEE16414}" name="Location" dataDxfId="95"/>
+    <tableColumn id="11" xr3:uid="{90463963-07D5-41E4-BF61-BFD7B42D2A8F}" name="Notes" dataDxfId="94"/>
+    <tableColumn id="12" xr3:uid="{C591FF9E-CAEC-4B9E-9E09-27AF2E069563}" name="QR Applied" dataDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{67265275-5EEA-4462-A9DC-E2989E840827}" name="Pumps" displayName="Pumps" ref="A1:L35" totalsRowShown="0" headerRowDxfId="72">
-  <autoFilter ref="A1:L35" xr:uid="{67265275-5EEA-4462-A9DC-E2989E840827}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L35">
-    <sortCondition ref="B1:B35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{67265275-5EEA-4462-A9DC-E2989E840827}" name="Pumps" displayName="Pumps" ref="A1:L37" totalsRowShown="0" headerRowDxfId="67">
+  <autoFilter ref="A1:L37" xr:uid="{67265275-5EEA-4462-A9DC-E2989E840827}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L37">
+    <sortCondition ref="A1:A37"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{1BE48298-1B91-4744-B3D3-BA050AC2ACFD}" name="SAGE REFERENCE" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{4361A13A-1C0E-4041-A030-F8B6A5049A1A}" name="Equipment type " dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{1BE48298-1B91-4744-B3D3-BA050AC2ACFD}" name="SAGE REFERENCE" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{4361A13A-1C0E-4041-A030-F8B6A5049A1A}" name="Equipment type " dataDxfId="65"/>
     <tableColumn id="3" xr3:uid="{1410BC8F-319B-413D-9750-2DF21C5104C5}" name="Model "/>
-    <tableColumn id="4" xr3:uid="{9A33259E-1B32-469E-96CA-0AC38B70E7E1}" name="Serial Number" dataDxfId="69"/>
-    <tableColumn id="5" xr3:uid="{0A0B60EC-CBD9-41EE-B828-D30664154015}" name="Date into Service" dataDxfId="68"/>
-    <tableColumn id="6" xr3:uid="{A1796AD3-051E-44A1-BD78-8586A5CF03F3}" name="Last Service" dataDxfId="67"/>
-    <tableColumn id="7" xr3:uid="{B5B6D5BC-6114-4BBB-B306-294ACAD488AE}" name="Next Service" dataDxfId="66">
-      <calculatedColumnFormula>EDATE(F2,6)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{CEC7940B-1955-48EE-B0B2-374E88B1714C}" name="Service status" dataDxfId="65">
-      <calculatedColumnFormula>IF(G2&lt;TODAY(),"Service overdue","In Service")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{606DAEDD-1E85-49C5-9139-2565DADF64D7}" name="Days to next service" dataDxfId="64">
-      <calculatedColumnFormula>IF((G2-TODAY())&gt;0,(G2-TODAY()),"N/a")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{CDC6DD74-02CA-4BC2-A2AE-5F3CCEBFCAB7}" name="Location" dataDxfId="63"/>
-    <tableColumn id="11" xr3:uid="{FEC82889-F1E7-4DEA-9649-67DAB0E24C8B}" name="Notes" dataDxfId="62"/>
-    <tableColumn id="12" xr3:uid="{E0E8DE59-8C63-4D3B-8ECF-AE97D0D7841B}" name="QR Applied" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{9A33259E-1B32-469E-96CA-0AC38B70E7E1}" name="Serial Number" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{0A0B60EC-CBD9-41EE-B828-D30664154015}" name="Date into Service" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{A1796AD3-051E-44A1-BD78-8586A5CF03F3}" name="Last Service" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{B5B6D5BC-6114-4BBB-B306-294ACAD488AE}" name="Next Service" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{CEC7940B-1955-48EE-B0B2-374E88B1714C}" name="Service status" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{606DAEDD-1E85-49C5-9139-2565DADF64D7}" name="Days to next service" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{CDC6DD74-02CA-4BC2-A2AE-5F3CCEBFCAB7}" name="Location" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{FEC82889-F1E7-4DEA-9649-67DAB0E24C8B}" name="Notes" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{E0E8DE59-8C63-4D3B-8ECF-AE97D0D7841B}" name="QR Applied" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5264EB1D-0653-4FBA-BE40-AF3278217271}" name="Subs" displayName="Subs" ref="A1:L28" totalsRowShown="0" headerRowDxfId="60">
-  <autoFilter ref="A1:L28" xr:uid="{5264EB1D-0653-4FBA-BE40-AF3278217271}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5264EB1D-0653-4FBA-BE40-AF3278217271}" name="Subs" displayName="Subs" ref="A1:L31" totalsRowShown="0" headerRowDxfId="154">
+  <autoFilter ref="A1:L31" xr:uid="{5264EB1D-0653-4FBA-BE40-AF3278217271}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L31">
+    <sortCondition ref="A1:A31"/>
+  </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{94F05F34-F349-4181-A542-E52629C9E211}" name="SAGE REFERENCE" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{B2998673-879F-462C-B926-F678E0D52D3C}" name="Equipment type " dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{390F5B0D-42AB-41CD-A60C-1968F68454DF}" name="Model " dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{9DD80FAC-5B50-493A-9407-465B86E399D4}" name="Serial Number" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{40E0B144-4F24-4AED-9991-D68BC84D18F8}" name="Date into Service" dataDxfId="55"/>
-    <tableColumn id="6" xr3:uid="{FE144FC2-5CD5-4A35-BEF7-F5433E635BFA}" name="Last Service" dataDxfId="54"/>
-    <tableColumn id="7" xr3:uid="{E115D80D-1021-419C-8E36-14132EEE8DB3}" name="Next Service" dataDxfId="53"/>
-    <tableColumn id="8" xr3:uid="{B56BBCEC-2EA7-4FC8-8C0F-4867CD1B2D62}" name="Service status" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{EA3C5FC1-1FDD-4A20-B085-615154512CA5}" name="Days to next service" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{91115C14-BB48-43C1-91A7-8EECC8D4C95E}" name="Location" dataDxfId="50"/>
-    <tableColumn id="11" xr3:uid="{CFD7031D-6696-4A9F-B4B4-6C1502D766D0}" name="Notes" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{16D13AE1-A43C-4D23-926B-FFF963A1206D}" name="QR Applied" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{94F05F34-F349-4181-A542-E52629C9E211}" name="SAGE REFERENCE" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{B2998673-879F-462C-B926-F678E0D52D3C}" name="Equipment type " dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{390F5B0D-42AB-41CD-A60C-1968F68454DF}" name="Model " dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{9DD80FAC-5B50-493A-9407-465B86E399D4}" name="Serial Number" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{40E0B144-4F24-4AED-9991-D68BC84D18F8}" name="Date into Service" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{FE144FC2-5CD5-4A35-BEF7-F5433E635BFA}" name="Last Service" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{E115D80D-1021-419C-8E36-14132EEE8DB3}" name="Next Service" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{B56BBCEC-2EA7-4FC8-8C0F-4867CD1B2D62}" name="Service status" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{EA3C5FC1-1FDD-4A20-B085-615154512CA5}" name="Days to next service" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{91115C14-BB48-43C1-91A7-8EECC8D4C95E}" name="Location" dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{CFD7031D-6696-4A9F-B4B4-6C1502D766D0}" name="Notes" dataDxfId="28"/>
+    <tableColumn id="12" xr3:uid="{16D13AE1-A43C-4D23-926B-FFF963A1206D}" name="QR Applied" dataDxfId="153"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3CB46473-0F56-4697-9E05-105E91D7F79C}" name="Dosing" displayName="Dosing" ref="A1:K9" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" tableBorderDxfId="45">
-  <autoFilter ref="A1:K9" xr:uid="{3CB46473-0F56-4697-9E05-105E91D7F79C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3CB46473-0F56-4697-9E05-105E91D7F79C}" name="Dosing" displayName="Dosing" ref="A1:K10" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:K10" xr:uid="{3CB46473-0F56-4697-9E05-105E91D7F79C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K10">
+    <sortCondition ref="A1:A10"/>
+  </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{78FBB022-4BB0-4456-A165-7CCF3961FC50}" name="SAGE REFERENCE" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{1357E97B-6CCF-4EDD-A644-D2EFA80150B6}" name="Equipment type " dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{A7FDDD8B-EEE1-4643-BF76-6562F3C57913}" name="Model " dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{17707999-51FA-45D4-89F9-28C44EA09143}" name="Serial Number" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{A621761E-8987-49F7-A3C9-95D450D627CB}" name="Date into Service" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{F77E0786-880E-4E7B-B155-07D0C2AF24EF}" name="Last Service" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{CC5D4B36-C3BE-4201-B836-4DCC3F9050FB}" name="Next Service" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{8B04D38A-1842-408A-904F-30CA73458362}" name="Service status" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{D86BD887-89A0-4456-B6A9-E6800690CAC8}" name="Days to next service" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{5E10A458-67BF-4206-BB92-B826AC314BFD}" name="Location" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{BECA969B-8F29-4B41-8ACC-1560629B4A30}" name="Notes" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{78FBB022-4BB0-4456-A165-7CCF3961FC50}" name="SAGE REFERENCE" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{1357E97B-6CCF-4EDD-A644-D2EFA80150B6}" name="Equipment type " dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{A7FDDD8B-EEE1-4643-BF76-6562F3C57913}" name="Model " dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{17707999-51FA-45D4-89F9-28C44EA09143}" name="Serial Number" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{A621761E-8987-49F7-A3C9-95D450D627CB}" name="Date into Service" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{F77E0786-880E-4E7B-B155-07D0C2AF24EF}" name="Last Service" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{CC5D4B36-C3BE-4201-B836-4DCC3F9050FB}" name="Next Service" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{8B04D38A-1842-408A-904F-30CA73458362}" name="Service status" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{D86BD887-89A0-4456-B6A9-E6800690CAC8}" name="Days to next service" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{5E10A458-67BF-4206-BB92-B826AC314BFD}" name="Location" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{BECA969B-8F29-4B41-8ACC-1560629B4A30}" name="Notes" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3020,7 +3649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5432F16-B5F3-44C1-B803-E23F41653FF2}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
@@ -3076,148 +3705,140 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>17</v>
+      <c r="A2" s="7">
+        <v>6083</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="7"/>
+        <v>79</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>205</v>
+      </c>
       <c r="D2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="13">
-        <v>42317</v>
+        <v>206</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="F2" s="9">
-        <v>45884</v>
+        <v>46127</v>
       </c>
       <c r="G2" s="10">
-        <f>EDATE(F2,6)</f>
-        <v>46068</v>
-      </c>
-      <c r="H2" s="7" t="str">
-        <f t="shared" ref="H2:H28" ca="1" si="0">IF(G2&lt;TODAY(),"Service overdue","In Service")</f>
-        <v>Service overdue</v>
-      </c>
-      <c r="I2" s="7" t="str">
-        <f t="shared" ref="I2:I28" ca="1" si="1">IF((G2-TODAY())&gt;0,(G2-TODAY()),"N/a")</f>
-        <v>N/a</v>
+        <v>46310</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I2" s="7">
+        <v>92</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="57">
-        <v>42801</v>
+        <v>18</v>
+      </c>
+      <c r="E3" s="56">
+        <v>42317</v>
       </c>
       <c r="F3" s="9">
-        <v>45748</v>
+        <v>46086</v>
       </c>
       <c r="G3" s="10">
-        <f>EDATE(F3,12)</f>
-        <v>46113</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I3" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
+        <v>46270</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I3" s="7">
+        <v>52</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>82</v>
+      <c r="A4" s="17" t="s">
+        <v>73</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C4" s="7"/>
-      <c r="D4" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="57">
+      <c r="D4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="8">
         <v>42801</v>
       </c>
       <c r="F4" s="9">
-        <v>45748</v>
+        <v>46127</v>
       </c>
       <c r="G4" s="10">
-        <f>EDATE(F4,12)</f>
-        <v>46113</v>
-      </c>
-      <c r="H4" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I4" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
+        <v>46310</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I4" s="7">
+        <v>92</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>29</v>
       </c>
       <c r="K4" s="7"/>
-      <c r="L4" s="11" t="b">
-        <v>0</v>
+      <c r="L4" s="15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>15</v>
+      <c r="D5" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="8">
+        <v>42801</v>
       </c>
       <c r="F5" s="9">
-        <v>45782</v>
+        <v>45748</v>
       </c>
       <c r="G5" s="10">
-        <f>EDATE(F5,6)</f>
-        <v>45966</v>
-      </c>
-      <c r="H5" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I5" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
-      </c>
-      <c r="J5" s="7"/>
+        <v>46113</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>19</v>
+      </c>
       <c r="K5" s="7" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="L5" s="11" t="b">
         <v>0</v>
@@ -3225,148 +3846,138 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>23</v>
+        <v>14</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="F6" s="9">
-        <v>45894</v>
+        <v>45782</v>
       </c>
       <c r="G6" s="10">
-        <f>EDATE(F6,6)</f>
-        <v>46078</v>
-      </c>
-      <c r="H6" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I6" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="7"/>
+        <v>45966</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="L6" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>27</v>
+      <c r="A7" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="D7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="8">
-        <v>44901</v>
+        <v>22</v>
+      </c>
+      <c r="E7" s="56" t="s">
+        <v>23</v>
       </c>
       <c r="F7" s="9">
-        <v>45770</v>
+        <v>46090</v>
       </c>
       <c r="G7" s="10">
-        <f>EDATE(F7,12)</f>
-        <v>46135</v>
-      </c>
-      <c r="H7" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46274</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I7" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>30</v>
+        <v>197</v>
       </c>
       <c r="L7" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="14" t="s">
-        <v>32</v>
+      <c r="D8" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="E8" s="8">
         <v>44901</v>
       </c>
       <c r="F8" s="9">
-        <v>45770</v>
+        <v>46136</v>
       </c>
       <c r="G8" s="10">
-        <f>EDATE(F8,12)</f>
-        <v>46135</v>
-      </c>
-      <c r="H8" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46319</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I8" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E9" s="8">
         <v>44901</v>
       </c>
       <c r="F9" s="9">
-        <v>46071</v>
+        <v>46126</v>
       </c>
       <c r="G9" s="10">
-        <f t="shared" ref="G9:G22" si="2">EDATE(F9,6)</f>
-        <v>46252</v>
-      </c>
-      <c r="H9" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46309</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="11" t="b">
@@ -3375,502 +3986,467 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>86</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C10" s="7"/>
       <c r="D10" s="7" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="E10" s="8">
-        <v>45017</v>
+        <v>44901</v>
       </c>
       <c r="F10" s="9">
-        <v>45938</v>
+        <v>46071</v>
       </c>
       <c r="G10" s="10">
-        <f t="shared" si="2"/>
-        <v>46120</v>
-      </c>
-      <c r="H10" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46252</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I10" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>44</v>
+        <v>80</v>
+      </c>
+      <c r="D11" s="60" t="s">
+        <v>81</v>
       </c>
       <c r="E11" s="8">
-        <v>45099</v>
+        <v>45017</v>
       </c>
       <c r="F11" s="9">
-        <v>45894</v>
+        <v>46154</v>
       </c>
       <c r="G11" s="10">
-        <f t="shared" si="2"/>
-        <v>46078</v>
-      </c>
-      <c r="H11" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I11" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
+        <v>46338</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I11" s="7">
+        <v>120</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>24</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>74</v>
+      <c r="A12" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>75</v>
+        <v>41</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>42</v>
       </c>
       <c r="E12" s="8">
-        <v>45372</v>
+        <v>45099</v>
       </c>
       <c r="F12" s="9">
-        <v>45884</v>
+        <v>46079</v>
       </c>
       <c r="G12" s="10">
-        <f t="shared" si="2"/>
-        <v>46068</v>
-      </c>
-      <c r="H12" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I12" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
-      </c>
-      <c r="J12" s="7"/>
+        <v>46260</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I12" s="7">
+        <v>42</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>19</v>
+      </c>
       <c r="K12" s="7" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="L12" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>35</v>
+      <c r="D13" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="E13" s="8">
-        <v>45425</v>
+        <v>45372</v>
       </c>
       <c r="F13" s="9">
-        <v>46048</v>
+        <v>46086</v>
       </c>
       <c r="G13" s="10">
-        <f t="shared" si="2"/>
-        <v>46229</v>
-      </c>
-      <c r="H13" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46270</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I13" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="15" t="b">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>34</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="E14" s="8">
         <v>45425</v>
       </c>
       <c r="F14" s="9">
-        <v>45894</v>
+        <v>46048</v>
       </c>
       <c r="G14" s="10">
-        <f t="shared" si="2"/>
-        <v>46078</v>
-      </c>
-      <c r="H14" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I14" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
-      </c>
-      <c r="J14" s="7"/>
+        <v>46229</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I14" s="7">
+        <v>11</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>198</v>
+      </c>
       <c r="K14" s="7"/>
       <c r="L14" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="E15" s="8">
         <v>45425</v>
       </c>
       <c r="F15" s="9">
-        <v>45803</v>
+        <v>46212</v>
       </c>
       <c r="G15" s="10">
-        <f t="shared" si="2"/>
-        <v>45987</v>
-      </c>
-      <c r="H15" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I15" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
+        <v>46396</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I15" s="7">
+        <v>178</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>24</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>52</v>
+        <v>33</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="E16" s="8">
         <v>45425</v>
       </c>
       <c r="F16" s="9">
-        <v>46071</v>
+        <v>46079</v>
       </c>
       <c r="G16" s="10">
-        <f t="shared" si="2"/>
-        <v>46252</v>
-      </c>
-      <c r="H16" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46260</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I16" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>49</v>
-      </c>
       <c r="E17" s="8">
-        <v>45446</v>
+        <v>45425</v>
       </c>
       <c r="F17" s="9">
-        <v>45756</v>
+        <v>46071</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" si="2"/>
-        <v>45939</v>
-      </c>
-      <c r="H17" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I17" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
-      </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7" t="s">
-        <v>50</v>
-      </c>
+        <v>46252</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I17" s="7">
+        <v>34</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="7"/>
       <c r="L17" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>55</v>
+        <v>41</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="E18" s="8">
         <v>45446</v>
       </c>
       <c r="F18" s="9">
-        <v>46010</v>
+        <v>46134</v>
       </c>
       <c r="G18" s="10">
-        <f t="shared" si="2"/>
-        <v>46192</v>
-      </c>
-      <c r="H18" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46317</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K18" s="7"/>
-      <c r="L18" s="11" t="b">
+      <c r="L18" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>46</v>
+        <v>33</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="E19" s="8">
+        <v>45446</v>
+      </c>
+      <c r="F19" s="9">
+        <v>46010</v>
+      </c>
+      <c r="G19" s="10">
+        <v>46192</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="L19" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="8">
         <v>45499</v>
       </c>
-      <c r="F19" s="9">
-        <v>45884</v>
-      </c>
-      <c r="G19" s="10">
-        <f t="shared" si="2"/>
-        <v>46068</v>
-      </c>
-      <c r="H19" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I19" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="11" t="b">
+      <c r="F20" s="9">
+        <v>46086</v>
+      </c>
+      <c r="G20" s="10">
+        <v>46270</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I20" s="7">
+        <v>52</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="L20" s="11" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="8">
-        <v>45552</v>
-      </c>
-      <c r="F20" s="9">
-        <v>45938</v>
-      </c>
-      <c r="G20" s="10">
-        <f t="shared" si="2"/>
-        <v>46120</v>
-      </c>
-      <c r="H20" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
-      </c>
-      <c r="I20" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="L20" s="11" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>73</v>
-      </c>
       <c r="E21" s="8">
-        <v>45594</v>
+        <v>45552</v>
       </c>
       <c r="F21" s="9">
-        <v>45960</v>
+        <v>46086</v>
       </c>
       <c r="G21" s="10">
-        <f t="shared" si="2"/>
-        <v>46142</v>
-      </c>
-      <c r="H21" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46270</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I21" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>24</v>
+        <v>210</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E22" s="8">
-        <v>45674</v>
+        <v>45594</v>
       </c>
       <c r="F22" s="9">
-        <v>46071</v>
+        <v>46212</v>
       </c>
       <c r="G22" s="10">
-        <f t="shared" si="2"/>
-        <v>46252</v>
-      </c>
-      <c r="H22" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46396</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>24</v>
@@ -3882,115 +4458,106 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="8">
+        <v>45674</v>
+      </c>
+      <c r="F23" s="9">
+        <v>46071</v>
+      </c>
+      <c r="G23" s="10">
+        <v>46252</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I23" s="7">
         <v>34</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="8">
-        <v>45734</v>
-      </c>
-      <c r="F23" s="9">
-        <v>45748</v>
-      </c>
-      <c r="G23" s="10">
-        <f>EDATE(F23,12)</f>
-        <v>46113</v>
-      </c>
-      <c r="H23" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I23" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
-      </c>
       <c r="J23" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>67</v>
+        <v>33</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="E24" s="8">
         <v>45734</v>
       </c>
       <c r="F24" s="9">
-        <v>45748</v>
+        <v>46118</v>
       </c>
       <c r="G24" s="10">
-        <f>EDATE(F24,12)</f>
-        <v>46113</v>
-      </c>
-      <c r="H24" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I24" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
+        <v>46301</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I24" s="7">
+        <v>83</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>29</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>59</v>
+        <v>33</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="E25" s="19">
-        <v>45689</v>
+        <v>45734</v>
       </c>
       <c r="F25" s="9">
-        <v>45938</v>
+        <v>46118</v>
       </c>
       <c r="G25" s="10">
-        <f>EDATE(F25,6)</f>
-        <v>46120</v>
-      </c>
-      <c r="H25" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
+        <v>46301</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="I25" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="11" t="b">
@@ -3999,149 +4566,216 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="62" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="59">
+        <v>33</v>
+      </c>
+      <c r="D26" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="57">
         <v>45689</v>
       </c>
       <c r="F26" s="20">
-        <v>45716</v>
+        <v>46154</v>
       </c>
       <c r="G26" s="10">
-        <f>EDATE(F26,6)</f>
-        <v>45897</v>
-      </c>
-      <c r="H26" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I26" s="7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>N/a</v>
-      </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7" t="s">
-        <v>62</v>
-      </c>
+        <v>46338</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I26" s="7">
+        <v>120</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="K26" s="7"/>
       <c r="L26" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="58">
-        <v>45860</v>
+        <v>33</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="63">
+        <v>45689</v>
       </c>
       <c r="F27" s="9">
-        <v>46071</v>
+        <v>45716</v>
       </c>
       <c r="G27" s="10">
-        <f>EDATE(F27,6)</f>
-        <v>46252</v>
-      </c>
-      <c r="H27" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
-      </c>
-      <c r="I27" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>137</v>
+        <v>45897</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>213</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="L27" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
+      <c r="A28" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="B28" s="7" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="8">
+        <v>45860</v>
+      </c>
+      <c r="F28" s="9">
+        <v>46071</v>
+      </c>
+      <c r="G28" s="10">
+        <v>46252</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I28" s="7">
         <v>34</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="8">
+      <c r="J28" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="E29" s="19">
+        <v>46090</v>
+      </c>
+      <c r="F29" s="9">
+        <v>46156</v>
+      </c>
+      <c r="G29" s="10">
+        <v>46340</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I29" s="7">
+        <v>122</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="L29" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="58">
         <v>45292</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F30" s="9">
         <v>46055</v>
       </c>
-      <c r="G28" s="10">
-        <f>EDATE(F28,6)</f>
+      <c r="G30" s="10">
         <v>46236</v>
       </c>
-      <c r="H28" s="7" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>In Service</v>
-      </c>
-      <c r="I28" s="7">
-        <f t="shared" ca="1" si="1"/>
-        <v>121</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="15" t="b">
-        <v>1</v>
+      <c r="H30" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I30" s="7">
+        <v>18</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="L30" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A28">
-    <cfRule type="containsBlanks" dxfId="33" priority="7">
+  <conditionalFormatting sqref="A1:A30">
+    <cfRule type="containsBlanks" dxfId="152" priority="7">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E28">
-    <cfRule type="containsText" dxfId="32" priority="4" operator="containsText" text="Pre 2020">
+  <conditionalFormatting sqref="E1:E30">
+    <cfRule type="containsText" dxfId="151" priority="4" operator="containsText" text="Pre 2020">
       <formula>NOT(ISERROR(SEARCH("Pre 2020",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G28">
-    <cfRule type="expression" dxfId="31" priority="11">
+  <conditionalFormatting sqref="G2:G30">
+    <cfRule type="expression" dxfId="150" priority="11">
       <formula>G2&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="12">
+    <cfRule type="expression" dxfId="149" priority="12">
       <formula>G2&gt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H28">
-    <cfRule type="expression" dxfId="29" priority="9">
+  <conditionalFormatting sqref="H2:H30">
+    <cfRule type="expression" dxfId="148" priority="9">
       <formula>G2&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="10">
+    <cfRule type="expression" dxfId="147" priority="10">
       <formula>G2&gt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I28">
+  <conditionalFormatting sqref="I2:I30">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -4151,27 +4785,27 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J28">
-    <cfRule type="containsText" dxfId="27" priority="8" operator="containsText" text="Wales">
+  <conditionalFormatting sqref="J1:J30">
+    <cfRule type="containsText" dxfId="146" priority="8" operator="containsText" text="Wales">
       <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K28">
-    <cfRule type="containsText" dxfId="26" priority="5" operator="containsText" text="QR">
+  <conditionalFormatting sqref="K1:K30">
+    <cfRule type="containsText" dxfId="145" priority="5" operator="containsText" text="QR">
       <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="6" operator="containsText" text="Set for service">
+    <cfRule type="containsText" dxfId="144" priority="6" operator="containsText" text="Set for service">
       <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L28">
-    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="FALSE">
+  <conditionalFormatting sqref="L2:L30">
+    <cfRule type="containsText" dxfId="143" priority="1" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="2" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="142" priority="2" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="IDK">
+    <cfRule type="containsText" dxfId="141" priority="3" operator="containsText" text="IDK">
       <formula>NOT(ISERROR(SEARCH("IDK",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4185,7 +4819,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05FAD95E-4EAE-445E-95FE-33429B9AA9ED}">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
@@ -4241,38 +4875,33 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
-        <v>110</v>
+      <c r="A2" s="22">
+        <v>2802</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>90</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="C2" s="22"/>
       <c r="D2" s="22" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F2" s="23">
-        <v>45894</v>
+        <v>46127</v>
       </c>
       <c r="G2" s="24">
-        <f t="shared" ref="G2:G20" si="0">EDATE(F2,6)</f>
-        <v>46078</v>
-      </c>
-      <c r="H2" s="22" t="str">
-        <f t="shared" ref="H2:H35" ca="1" si="1">IF(G2&lt;TODAY(),"Service overdue","In Service")</f>
-        <v>Service overdue</v>
-      </c>
-      <c r="I2" s="22" t="str">
-        <f t="shared" ref="I2:I35" ca="1" si="2">IF((G2-TODAY())&gt;0,(G2-TODAY()),"N/a")</f>
-        <v>N/a</v>
+        <v>46310</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I2" s="22">
+        <v>92</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="K2" s="22"/>
       <c r="L2" s="11" t="b">
@@ -4280,175 +4909,163 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>115</v>
+      <c r="A3" s="25">
+        <v>3402</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>116</v>
+        <v>84</v>
+      </c>
+      <c r="D3" s="66" t="s">
+        <v>114</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="26">
-        <v>45960</v>
+        <v>46118</v>
       </c>
       <c r="G3" s="27">
-        <f t="shared" si="0"/>
-        <v>46142</v>
-      </c>
-      <c r="H3" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46301</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I3" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K3" s="25"/>
-      <c r="L3" s="11" t="b">
+      <c r="L3" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F4" s="26">
-        <v>46010</v>
+        <v>46139</v>
       </c>
       <c r="G4" s="24">
-        <f t="shared" si="0"/>
-        <v>46192</v>
-      </c>
-      <c r="H4" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46322</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I4" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="J4" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="25" t="s">
-        <v>114</v>
-      </c>
+      <c r="K4" s="25"/>
       <c r="L4" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="26">
-        <v>45938</v>
+        <v>46154</v>
       </c>
       <c r="G5" s="24">
-        <f t="shared" si="0"/>
-        <v>46120</v>
-      </c>
-      <c r="H5" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46338</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I5" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="25"/>
+        <v>216</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>217</v>
+      </c>
       <c r="L5" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="E6" s="26" t="s">
+      <c r="A6" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="26">
-        <v>45736</v>
-      </c>
-      <c r="G6" s="27">
-        <f t="shared" si="0"/>
-        <v>45920</v>
-      </c>
-      <c r="H6" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I6" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
-      </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="25" t="s">
-        <v>133</v>
-      </c>
+      <c r="F6" s="30">
+        <v>46212</v>
+      </c>
+      <c r="G6" s="31">
+        <v>46396</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" s="28">
+        <v>178</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="28"/>
       <c r="L6" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>15</v>
@@ -4457,254 +5074,235 @@
         <v>46048</v>
       </c>
       <c r="G7" s="27">
-        <f t="shared" si="0"/>
         <v>46229</v>
       </c>
-      <c r="H7" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+      <c r="H7" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I7" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="J7" s="22" t="s">
         <v>24</v>
       </c>
       <c r="K7" s="25"/>
-      <c r="L7" s="15" t="b">
+      <c r="L7" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="26">
-        <v>44562</v>
+        <v>113</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>15</v>
       </c>
       <c r="F8" s="9">
-        <v>45756</v>
+        <v>46139</v>
       </c>
       <c r="G8" s="27">
-        <f t="shared" si="0"/>
-        <v>45939</v>
-      </c>
-      <c r="H8" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I8" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="L8" s="11" t="b">
-        <v>0</v>
+        <v>46322</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I8" s="25">
+        <v>104</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="25"/>
+      <c r="L8" s="15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F9" s="26">
-        <v>45960</v>
+        <v>45894</v>
       </c>
       <c r="G9" s="27">
-        <f t="shared" si="0"/>
-        <v>46142</v>
-      </c>
-      <c r="H9" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I9" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="25"/>
+        <v>46078</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="J9" s="22"/>
+      <c r="K9" s="25" t="s">
+        <v>225</v>
+      </c>
       <c r="L9" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" s="26">
-        <v>44287</v>
+        <v>136</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>15</v>
       </c>
       <c r="F10" s="26">
-        <v>45736</v>
+        <v>46134</v>
       </c>
       <c r="G10" s="27">
-        <f t="shared" si="0"/>
-        <v>45920</v>
-      </c>
-      <c r="H10" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I10" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
-      </c>
-      <c r="J10" s="22"/>
-      <c r="K10" s="25" t="s">
-        <v>133</v>
-      </c>
+        <v>46317</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" s="25">
+        <v>99</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="25"/>
       <c r="L10" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="26">
-        <v>46010</v>
+        <v>45736</v>
       </c>
       <c r="G11" s="24">
-        <f t="shared" si="0"/>
-        <v>46192</v>
-      </c>
-      <c r="H11" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I11" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+        <v>45920</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>213</v>
       </c>
       <c r="J11" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="25"/>
+        <v>19</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>123</v>
+      </c>
       <c r="L11" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="30" t="s">
+      <c r="A12" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="30">
-        <v>46010</v>
-      </c>
-      <c r="G12" s="31">
-        <f t="shared" si="0"/>
-        <v>46192</v>
-      </c>
-      <c r="H12" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I12" s="36">
-        <f t="shared" ca="1" si="2"/>
-        <v>77</v>
+      <c r="F12" s="26">
+        <v>46048</v>
+      </c>
+      <c r="G12" s="27">
+        <v>46229</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I12" s="22">
+        <v>11</v>
       </c>
       <c r="J12" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>119</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="K12" s="25"/>
       <c r="L12" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B13" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>98</v>
-      </c>
       <c r="E13" s="26">
-        <v>44999</v>
+        <v>44562</v>
       </c>
       <c r="F13" s="26">
-        <v>45938</v>
+        <v>46086</v>
       </c>
       <c r="G13" s="24">
-        <f t="shared" si="0"/>
-        <v>46120</v>
-      </c>
-      <c r="H13" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46270</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I13" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="J13" s="22"/>
+        <v>52</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>210</v>
+      </c>
       <c r="K13" s="25"/>
       <c r="L13" s="11" t="b">
         <v>1</v>
@@ -4712,572 +5310,539 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="63" t="s">
-        <v>93</v>
+        <v>121</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>128</v>
       </c>
       <c r="E14" s="26">
-        <v>45017</v>
+        <v>44743</v>
       </c>
       <c r="F14" s="26">
-        <v>46055</v>
+        <v>46139</v>
       </c>
       <c r="G14" s="27">
-        <f t="shared" si="0"/>
-        <v>46236</v>
-      </c>
-      <c r="H14" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46322</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I14" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="J14" s="22" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K14" s="25"/>
-      <c r="L14" s="15" t="b">
+      <c r="L14" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B15" s="25" t="s">
-        <v>89</v>
-      </c>
       <c r="C15" s="25" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="30">
-        <v>45797</v>
+        <v>130</v>
+      </c>
+      <c r="E15" s="26">
+        <v>44743</v>
+      </c>
+      <c r="F15" s="26">
+        <v>46118</v>
       </c>
       <c r="G15" s="24">
-        <f t="shared" si="0"/>
-        <v>45981</v>
-      </c>
-      <c r="H15" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I15" s="36" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
-      </c>
-      <c r="J15" s="22"/>
+        <v>46301</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I15" s="22">
+        <v>83</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>29</v>
+      </c>
       <c r="K15" s="25"/>
       <c r="L15" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="26">
-        <v>45426</v>
+        <v>85</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>23</v>
       </c>
       <c r="F16" s="26">
-        <v>46048</v>
+        <v>46139</v>
       </c>
       <c r="G16" s="24">
-        <f t="shared" si="0"/>
-        <v>46229</v>
-      </c>
-      <c r="H16" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46322</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I16" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="J16" s="22" t="s">
         <v>24</v>
       </c>
       <c r="K16" s="25"/>
-      <c r="L16" s="15" t="b">
+      <c r="L16" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>106</v>
+        <v>121</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>122</v>
       </c>
       <c r="E17" s="26">
-        <v>45502</v>
+        <v>44287</v>
       </c>
       <c r="F17" s="26">
-        <v>46055</v>
+        <v>45736</v>
       </c>
       <c r="G17" s="24">
-        <f t="shared" si="0"/>
-        <v>46236</v>
-      </c>
-      <c r="H17" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I17" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>121</v>
+        <v>45920</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>213</v>
       </c>
       <c r="J17" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" s="25"/>
-      <c r="L17" s="15" t="b">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="L17" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="26">
-        <v>45292</v>
-      </c>
-      <c r="F18" s="26">
-        <v>45938</v>
+        <v>111</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="30">
+        <v>46010</v>
       </c>
       <c r="G18" s="24">
-        <f t="shared" si="0"/>
-        <v>46120</v>
-      </c>
-      <c r="H18" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I18" s="22">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>46192</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>213</v>
       </c>
       <c r="J18" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="K18" s="25"/>
+        <v>24</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>215</v>
+      </c>
       <c r="L18" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" s="9">
-        <v>45687</v>
+        <v>84</v>
+      </c>
+      <c r="D19" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F19" s="9">
-        <v>46071</v>
+        <v>46212</v>
       </c>
       <c r="G19" s="33">
-        <f t="shared" si="0"/>
-        <v>46252</v>
-      </c>
-      <c r="H19" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46396</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I19" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="J19" s="22" t="s">
         <v>24</v>
       </c>
       <c r="K19" s="7"/>
-      <c r="L19" s="11" t="b">
+      <c r="L19" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E20" s="9">
-        <v>45860</v>
-      </c>
-      <c r="F20" s="9"/>
+        <v>44999</v>
+      </c>
+      <c r="F20" s="9">
+        <v>46139</v>
+      </c>
       <c r="G20" s="33">
-        <f t="shared" si="0"/>
-        <v>182</v>
-      </c>
-      <c r="H20" s="25" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I20" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
+        <v>46322</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="I20" s="25">
+        <v>104</v>
       </c>
       <c r="J20" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="26">
+        <v>45017</v>
+      </c>
+      <c r="F21" s="26">
+        <v>46055</v>
+      </c>
+      <c r="G21" s="10">
+        <v>46236</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="I21" s="25">
+        <v>18</v>
+      </c>
+      <c r="J21" s="22" t="s">
         <v>24</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="L20" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="26">
-        <v>45770</v>
-      </c>
-      <c r="G21" s="10">
-        <f>EDATE(F21,12)</f>
-        <v>46135</v>
-      </c>
-      <c r="H21" s="34" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I21" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>29</v>
       </c>
       <c r="K21" s="25"/>
       <c r="L21" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
+      <c r="A22" s="25" t="s">
+        <v>117</v>
+      </c>
       <c r="B22" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="25"/>
+        <v>83</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>84</v>
+      </c>
       <c r="D22" s="25" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="26">
-        <v>45748</v>
+        <v>46118</v>
       </c>
       <c r="G22" s="24">
-        <f>EDATE(F22,12)</f>
-        <v>46113</v>
-      </c>
-      <c r="H22" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I22" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
+        <v>46301</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I22" s="25">
+        <v>83</v>
       </c>
       <c r="J22" s="22" t="s">
         <v>29</v>
       </c>
       <c r="K22" s="25"/>
       <c r="L22" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>15</v>
+        <v>143</v>
+      </c>
+      <c r="E23" s="26">
+        <v>45292</v>
       </c>
       <c r="F23" s="26">
-        <v>46048</v>
+        <v>46079</v>
       </c>
       <c r="G23" s="27">
-        <f>EDATE(F23,6)</f>
-        <v>46229</v>
-      </c>
-      <c r="H23" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46260</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I23" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K23" s="25"/>
-      <c r="L23" s="15" t="b">
+      <c r="L23" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>15</v>
+        <v>93</v>
+      </c>
+      <c r="E24" s="26">
+        <v>45426</v>
       </c>
       <c r="F24" s="26">
-        <v>45894</v>
+        <v>46212</v>
       </c>
       <c r="G24" s="27">
-        <f>EDATE(F24,6)</f>
-        <v>46078</v>
-      </c>
-      <c r="H24" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I24" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
-      </c>
-      <c r="J24" s="22"/>
-      <c r="K24" s="25" t="s">
-        <v>150</v>
-      </c>
+        <v>46396</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I24" s="25">
+        <v>178</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="K24" s="25"/>
       <c r="L24" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>15</v>
+        <v>99</v>
+      </c>
+      <c r="E25" s="9">
+        <v>45502</v>
       </c>
       <c r="F25" s="9">
-        <v>45807</v>
+        <v>46055</v>
       </c>
       <c r="G25" s="10">
-        <f>EDATE(F25,12)</f>
-        <v>46172</v>
-      </c>
-      <c r="H25" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46236</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I25" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>29</v>
+        <v>198</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26" s="26">
-        <v>44743</v>
-      </c>
-      <c r="F26" s="26">
-        <v>45960</v>
-      </c>
-      <c r="G26" s="27">
-        <f>EDATE(F26,6)</f>
-        <v>46142</v>
-      </c>
-      <c r="H26" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I26" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+      <c r="A26" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="30">
+        <v>45529</v>
+      </c>
+      <c r="F26" s="30">
+        <v>46048</v>
+      </c>
+      <c r="G26" s="31">
+        <v>46229</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I26" s="28">
+        <v>11</v>
       </c>
       <c r="J26" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="25"/>
-      <c r="L26" s="11" t="b">
+      <c r="K26" s="28"/>
+      <c r="L26" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
-        <v>139</v>
+      <c r="A27" s="25" t="s">
+        <v>144</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E27" s="26">
-        <v>44743</v>
+        <v>45538</v>
       </c>
       <c r="F27" s="26">
-        <v>45894</v>
+        <v>46118</v>
       </c>
       <c r="G27" s="27">
-        <f>EDATE(F27,6)</f>
-        <v>46078</v>
-      </c>
-      <c r="H27" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I27" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
-      </c>
-      <c r="J27" s="22"/>
-      <c r="K27" s="25" t="s">
-        <v>141</v>
-      </c>
+        <v>46301</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I27" s="25">
+        <v>83</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="25"/>
       <c r="L27" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>90</v>
+        <v>127</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>84</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E28" s="26">
-        <v>45292</v>
+        <v>45538</v>
       </c>
       <c r="F28" s="26">
-        <v>45884</v>
+        <v>46091</v>
       </c>
       <c r="G28" s="27">
-        <f>EDATE(F28,6)</f>
-        <v>46068</v>
-      </c>
-      <c r="H28" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I28" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
+        <v>46275</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I28" s="25">
+        <v>57</v>
       </c>
       <c r="J28" s="22" t="s">
         <v>24</v>
@@ -5289,116 +5854,109 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="E29" s="26">
-        <v>45529</v>
+        <v>45292</v>
       </c>
       <c r="F29" s="26">
-        <v>46048</v>
+        <v>46154</v>
       </c>
       <c r="G29" s="27">
-        <f>EDATE(F29,6)</f>
-        <v>46229</v>
-      </c>
-      <c r="H29" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
+        <v>46338</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="I29" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J29" s="22" t="s">
-        <v>24</v>
+        <v>203</v>
       </c>
       <c r="K29" s="25"/>
-      <c r="L29" s="11" t="b">
-        <v>1</v>
+      <c r="L29" s="15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="E30" s="26">
-        <v>45538</v>
+        <v>45687</v>
       </c>
       <c r="F30" s="26">
-        <v>45748</v>
+        <v>46071</v>
       </c>
       <c r="G30" s="27">
-        <f>EDATE(F30,12)</f>
-        <v>46113</v>
-      </c>
-      <c r="H30" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I30" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
+        <v>46252</v>
+      </c>
+      <c r="H30" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I30" s="25">
+        <v>34</v>
       </c>
       <c r="J30" s="22" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K30" s="25"/>
       <c r="L30" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>159</v>
+        <v>101</v>
       </c>
       <c r="E31" s="26">
-        <v>45538</v>
+        <v>45860</v>
       </c>
       <c r="F31" s="26">
-        <v>45884</v>
+        <v>46032</v>
       </c>
       <c r="G31" s="27">
-        <f>EDATE(F31,6)</f>
-        <v>46068</v>
-      </c>
-      <c r="H31" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I31" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
-      </c>
-      <c r="J31" s="22"/>
+        <v>46213</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>49</v>
+      </c>
       <c r="K31" s="25" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="L31" s="11" t="b">
         <v>0</v>
@@ -5406,184 +5964,246 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>131</v>
+        <v>127</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>121</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E32" s="26">
         <v>45999</v>
       </c>
       <c r="F32" s="26">
-        <v>45999</v>
+        <v>46023</v>
       </c>
       <c r="G32" s="27">
-        <f>EDATE(F32,6)</f>
-        <v>46181</v>
-      </c>
-      <c r="H32" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I32" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>66</v>
+        <v>46204</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="I32" s="25" t="s">
+        <v>213</v>
       </c>
       <c r="J32" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K32" s="25" t="s">
-        <v>150</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="K32" s="25"/>
       <c r="L32" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="60"/>
-      <c r="B33" s="61" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" s="61" t="s">
-        <v>142</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" s="30">
-        <v>46048</v>
-      </c>
-      <c r="G33" s="31">
-        <f>EDATE(F33,6)</f>
-        <v>46229</v>
-      </c>
-      <c r="H33" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I33" s="28">
-        <f t="shared" ca="1" si="2"/>
-        <v>114</v>
+      <c r="A33" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="B33" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="66" t="s">
+        <v>219</v>
+      </c>
+      <c r="E33" s="26">
+        <v>46073</v>
+      </c>
+      <c r="F33" s="26">
+        <v>46074</v>
+      </c>
+      <c r="G33" s="27">
+        <v>46255</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I33" s="25">
+        <v>37</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K33" s="28"/>
+        <v>19</v>
+      </c>
+      <c r="K33" s="25"/>
       <c r="L33" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="25"/>
+      <c r="A34" s="25" t="s">
+        <v>220</v>
+      </c>
       <c r="B34" s="25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>90</v>
+        <v>221</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" s="26">
-        <v>45960</v>
-      </c>
-      <c r="G34" s="27">
-        <f>EDATE(F34,6)</f>
-        <v>46142</v>
-      </c>
-      <c r="H34" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>In Service</v>
-      </c>
-      <c r="I34" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>27</v>
+        <v>222</v>
+      </c>
+      <c r="E34" s="26">
+        <v>46090</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="G34" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="H34" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>223</v>
       </c>
       <c r="J34" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="25"/>
+      <c r="K34" s="25" t="s">
+        <v>224</v>
+      </c>
       <c r="L34" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
+      <c r="A35" s="28"/>
       <c r="B35" s="25" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>15</v>
       </c>
       <c r="F35" s="26">
-        <v>45748</v>
+        <v>46048</v>
       </c>
       <c r="G35" s="27">
-        <f>EDATE(F35,12)</f>
-        <v>46113</v>
-      </c>
-      <c r="H35" s="22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Service overdue</v>
-      </c>
-      <c r="I35" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>N/a</v>
+        <v>46229</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="I35" s="25">
+        <v>11</v>
       </c>
       <c r="J35" s="22" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K35" s="25"/>
       <c r="L35" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="25"/>
+      <c r="B36" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="66" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="26">
+        <v>46139</v>
+      </c>
+      <c r="G36" s="27">
+        <v>46322</v>
+      </c>
+      <c r="H36" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="I36" s="25">
+        <v>104</v>
+      </c>
+      <c r="J36" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="25"/>
+      <c r="L36" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="25"/>
+      <c r="B37" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="66" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="26">
+        <v>45748</v>
+      </c>
+      <c r="G37" s="27">
+        <v>46113</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="I37" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="L37" s="11" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A35">
-    <cfRule type="containsBlanks" dxfId="21" priority="4">
+  <conditionalFormatting sqref="A1:A37">
+    <cfRule type="containsBlanks" dxfId="140" priority="4">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E35">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Pre 2020">
+  <conditionalFormatting sqref="E1:E37">
+    <cfRule type="containsText" dxfId="139" priority="1" operator="containsText" text="Pre 2020">
       <formula>NOT(ISERROR(SEARCH("Pre 2020",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G35">
-    <cfRule type="expression" dxfId="19" priority="16">
+  <conditionalFormatting sqref="G2:G37">
+    <cfRule type="expression" dxfId="138" priority="16">
       <formula>G2&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="17">
+    <cfRule type="expression" dxfId="137" priority="17">
       <formula>G2&gt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H35">
-    <cfRule type="expression" dxfId="17" priority="14">
+  <conditionalFormatting sqref="H2:H37">
+    <cfRule type="expression" dxfId="136" priority="14">
       <formula>G2&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="15">
+    <cfRule type="expression" dxfId="135" priority="15">
       <formula>G2&gt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I35">
+  <conditionalFormatting sqref="I2:I37">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -5593,27 +6213,27 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J35">
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="Wales">
+  <conditionalFormatting sqref="J1:J37">
+    <cfRule type="containsText" dxfId="134" priority="5" operator="containsText" text="Wales">
       <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K35">
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="QR">
+  <conditionalFormatting sqref="K1:K37">
+    <cfRule type="containsText" dxfId="133" priority="2" operator="containsText" text="QR">
       <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="Set for service">
+    <cfRule type="containsText" dxfId="132" priority="3" operator="containsText" text="Set for service">
       <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L35">
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="FALSE">
+  <conditionalFormatting sqref="L2:L37">
+    <cfRule type="containsText" dxfId="131" priority="6" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="130" priority="7" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="IDK">
+    <cfRule type="containsText" dxfId="129" priority="8" operator="containsText" text="IDK">
       <formula>NOT(ISERROR(SEARCH("IDK",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5627,7 +6247,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB49E92-200F-469A-8F69-4CD4530B239C}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
@@ -5684,10 +6304,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25">
@@ -5702,20 +6322,20 @@
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
       <c r="K2" s="25" t="s">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="L2" s="21"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C3" s="37"/>
       <c r="D3" s="38" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="E3" s="39">
         <v>42220</v>
@@ -5728,20 +6348,20 @@
         <v>24</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="L3" s="21"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C4" s="42"/>
       <c r="D4" s="43" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E4" s="44">
         <v>42128</v>
@@ -5754,20 +6374,18 @@
         <v>29</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="L4" s="21"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>215</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="B5" s="25"/>
       <c r="C5" s="42"/>
       <c r="D5" s="43" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="E5" s="44">
         <v>43536</v>
@@ -5780,20 +6398,18 @@
         <v>29</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="L5" s="21"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>215</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="B6" s="25"/>
       <c r="C6" s="42"/>
       <c r="D6" s="43" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="E6" s="44">
         <v>43536</v>
@@ -5810,16 +6426,16 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="E7" s="47">
         <v>44139</v>
@@ -5830,22 +6446,22 @@
       <c r="I7" s="22"/>
       <c r="J7" s="50"/>
       <c r="K7" s="46" t="s">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="L7" s="21"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="E8" s="48">
         <v>44139</v>
@@ -5855,15 +6471,17 @@
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
       <c r="J8" s="50"/>
-      <c r="K8" s="46"/>
+      <c r="K8" s="46" t="s">
+        <v>234</v>
+      </c>
       <c r="L8" s="21"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C9" s="46"/>
       <c r="D9" s="46">
@@ -5877,17 +6495,15 @@
       <c r="H9" s="22"/>
       <c r="I9" s="22"/>
       <c r="J9" s="50"/>
-      <c r="K9" s="37" t="s">
-        <v>182</v>
-      </c>
+      <c r="K9" s="37"/>
       <c r="L9" s="21"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C10" s="46"/>
       <c r="D10" s="46">
@@ -5906,10 +6522,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C11" s="46"/>
       <c r="D11" s="46">
@@ -5922,16 +6538,20 @@
       <c r="G11" s="49"/>
       <c r="H11" s="22"/>
       <c r="I11" s="22"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="46"/>
+      <c r="J11" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="46" t="s">
+        <v>235</v>
+      </c>
       <c r="L11" s="21"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C12" s="46"/>
       <c r="D12" s="46">
@@ -5950,10 +6570,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C13" s="46"/>
       <c r="D13" s="46">
@@ -5972,10 +6592,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="46">
@@ -5994,10 +6614,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C15" s="46"/>
       <c r="D15" s="46">
@@ -6016,10 +6636,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C16" s="46"/>
       <c r="D16" s="46">
@@ -6038,10 +6658,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C17" s="46"/>
       <c r="D17" s="46">
@@ -6060,10 +6680,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C18" s="46"/>
       <c r="D18" s="46">
@@ -6082,10 +6702,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C19" s="46"/>
       <c r="D19" s="46">
@@ -6098,16 +6718,18 @@
       <c r="G19" s="49"/>
       <c r="H19" s="22"/>
       <c r="I19" s="22"/>
-      <c r="J19" s="50"/>
+      <c r="J19" s="50" t="s">
+        <v>24</v>
+      </c>
       <c r="K19" s="46"/>
       <c r="L19" s="21"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="46">
@@ -6128,10 +6750,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="46">
@@ -6150,10 +6772,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="46">
@@ -6167,17 +6789,19 @@
       <c r="H22" s="22"/>
       <c r="I22" s="22"/>
       <c r="J22" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="K22" s="46"/>
+        <v>178</v>
+      </c>
+      <c r="K22" s="46" t="s">
+        <v>236</v>
+      </c>
       <c r="L22" s="21"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="46">
@@ -6196,10 +6820,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C24" s="46"/>
       <c r="D24" s="46">
@@ -6213,17 +6837,19 @@
       <c r="H24" s="22"/>
       <c r="I24" s="22"/>
       <c r="J24" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="K24" s="46"/>
+        <v>181</v>
+      </c>
+      <c r="K24" s="46" t="s">
+        <v>236</v>
+      </c>
       <c r="L24" s="21"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="46">
@@ -6236,22 +6862,24 @@
       <c r="G25" s="49"/>
       <c r="H25" s="22"/>
       <c r="I25" s="22"/>
-      <c r="J25" s="50"/>
+      <c r="J25" s="50" t="s">
+        <v>203</v>
+      </c>
       <c r="K25" s="46"/>
       <c r="L25" s="21"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C26" s="46" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="E26" s="48">
         <v>45644</v>
@@ -6263,23 +6891,21 @@
       <c r="J26" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="46" t="s">
-        <v>203</v>
-      </c>
+      <c r="K26" s="46"/>
       <c r="L26" s="21"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C27" s="46" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="E27" s="48">
         <v>45644</v>
@@ -6296,13 +6922,13 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C28" s="46" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="D28" s="46">
         <v>312593</v>
@@ -6320,29 +6946,99 @@
       <c r="K28" s="46"/>
       <c r="L28" s="21"/>
     </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="B29" s="70" t="s">
+        <v>232</v>
+      </c>
+      <c r="C29" s="70" t="s">
+        <v>238</v>
+      </c>
+      <c r="D29" s="70">
+        <v>3081620484</v>
+      </c>
+      <c r="E29" s="71">
+        <v>46030</v>
+      </c>
+      <c r="F29" s="71"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="21"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="B30" s="70" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" s="70" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="71">
+        <v>46072</v>
+      </c>
+      <c r="F30" s="71"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="21"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="B31" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="C31" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="46"/>
+      <c r="E31" s="48">
+        <v>46184</v>
+      </c>
+      <c r="F31" s="48"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="46"/>
+      <c r="L31" s="21"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A28">
-    <cfRule type="containsBlanks" dxfId="9" priority="4">
+  <conditionalFormatting sqref="A1:A31">
+    <cfRule type="containsBlanks" dxfId="128" priority="4">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E28">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Pre 2020">
+  <conditionalFormatting sqref="E1:E31">
+    <cfRule type="containsText" dxfId="127" priority="1" operator="containsText" text="Pre 2020">
       <formula>NOT(ISERROR(SEARCH("Pre 2020",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J28">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Wales">
+  <conditionalFormatting sqref="J1:J31">
+    <cfRule type="containsText" dxfId="126" priority="5" operator="containsText" text="Wales">
       <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:K2 K4:K28">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Set for service">
+    <cfRule type="containsText" dxfId="125" priority="3" operator="containsText" text="Set for service">
       <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K28">
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="QR">
+  <conditionalFormatting sqref="K1:K31">
+    <cfRule type="containsText" dxfId="124" priority="2" operator="containsText" text="QR">
       <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6356,7 +7052,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D76CA3-4BD1-4D66-86E0-AC494D5B91D6}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -6373,7 +7069,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -6408,119 +7104,109 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
-        <v>208</v>
+      <c r="A2" s="53" t="s">
+        <v>241</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="D2" s="28">
-        <v>2022337764</v>
+        <v>242</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28" t="s">
+        <v>152</v>
       </c>
       <c r="E2" s="30">
-        <v>44944</v>
+        <v>44480</v>
       </c>
       <c r="F2" s="30"/>
       <c r="G2" s="31"/>
       <c r="H2" s="28"/>
       <c r="I2" s="28"/>
       <c r="J2" s="28" t="s">
-        <v>24</v>
+        <v>243</v>
       </c>
       <c r="K2" s="28" t="s">
-        <v>76</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
-        <v>210</v>
+      <c r="A3" s="52" t="s">
+        <v>189</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>209</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C3" s="25"/>
       <c r="D3" s="25">
-        <v>2024246395</v>
+        <v>2022337764</v>
       </c>
       <c r="E3" s="26">
-        <v>45553</v>
+        <v>44944</v>
       </c>
       <c r="F3" s="26"/>
       <c r="G3" s="27"/>
       <c r="H3" s="25"/>
       <c r="I3" s="25"/>
       <c r="J3" s="25" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K3" s="25"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
-        <v>211</v>
+      <c r="A4" s="52" t="s">
+        <v>194</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>209</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C4" s="25"/>
       <c r="D4" s="25">
-        <v>2024246396</v>
+        <v>2024130073</v>
       </c>
       <c r="E4" s="26">
         <v>45553</v>
       </c>
       <c r="F4" s="26"/>
-      <c r="G4" s="25"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="25"/>
       <c r="I4" s="25"/>
       <c r="J4" s="25" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K4" s="25"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
-        <v>212</v>
+      <c r="A5" s="52" t="s">
+        <v>195</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>209</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C5" s="25"/>
       <c r="D5" s="25">
-        <v>2024251614</v>
+        <v>2024130074</v>
       </c>
       <c r="E5" s="26">
         <v>45553</v>
       </c>
       <c r="F5" s="26"/>
-      <c r="G5" s="25"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="J5" s="25" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K5" s="25"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
-        <v>213</v>
+      <c r="A6" s="52" t="s">
+        <v>191</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>209</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C6" s="25"/>
       <c r="D6" s="25">
-        <v>2024130073</v>
+        <v>2024246395</v>
       </c>
       <c r="E6" s="26">
         <v>45553</v>
@@ -6530,75 +7216,73 @@
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="J6" s="25" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K6" s="25"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
-        <v>214</v>
+      <c r="A7" s="52" t="s">
+        <v>192</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>209</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C7" s="25"/>
       <c r="D7" s="25">
-        <v>2024130074</v>
+        <v>2024246396</v>
       </c>
       <c r="E7" s="26">
         <v>45553</v>
       </c>
       <c r="F7" s="26"/>
-      <c r="G7" s="27"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="J7" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>76</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="K7" s="25"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
+      <c r="A8" s="52" t="s">
+        <v>193</v>
+      </c>
       <c r="B8" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>209</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C8" s="25"/>
       <c r="D8" s="25">
-        <v>2018292537</v>
+        <v>2024251614</v>
       </c>
       <c r="E8" s="26">
         <v>45553</v>
       </c>
       <c r="F8" s="26"/>
-      <c r="G8" s="27"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="J8" s="25" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
+      <c r="A9" s="54" t="s">
+        <v>246</v>
+      </c>
       <c r="B9" s="35" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="C9" s="35"/>
       <c r="D9" s="35">
-        <v>2014255293</v>
-      </c>
-      <c r="E9" s="56">
-        <v>45553</v>
-      </c>
-      <c r="F9" s="56"/>
+        <v>2025342006</v>
+      </c>
+      <c r="E9" s="55">
+        <v>46085</v>
+      </c>
+      <c r="F9" s="55"/>
       <c r="G9" s="33"/>
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
@@ -6607,14 +7291,37 @@
       </c>
       <c r="K9" s="35"/>
     </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="52"/>
+      <c r="B10" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25">
+        <v>2014255293</v>
+      </c>
+      <c r="E10" s="26">
+        <v>45553</v>
+      </c>
+      <c r="F10" s="26"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>248</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A9">
-    <cfRule type="containsBlanks" dxfId="4" priority="4">
+  <conditionalFormatting sqref="A1:A10">
+    <cfRule type="containsBlanks" dxfId="123" priority="4">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E9">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Pre 2020">
+  <conditionalFormatting sqref="E1:E10">
+    <cfRule type="containsText" dxfId="122" priority="1" operator="containsText" text="Pre 2020">
       <formula>NOT(ISERROR(SEARCH("Pre 2020",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6628,16 +7335,16 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J9">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Wales">
+  <conditionalFormatting sqref="J1:J10">
+    <cfRule type="containsText" dxfId="121" priority="5" operator="containsText" text="Wales">
       <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K9">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="QR">
+  <conditionalFormatting sqref="K1:K10">
+    <cfRule type="containsText" dxfId="120" priority="2" operator="containsText" text="QR">
       <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Set for service">
+    <cfRule type="containsText" dxfId="119" priority="3" operator="containsText" text="Set for service">
       <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6656,7 +7363,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/equipment_tables.xlsx
+++ b/equipment_tables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pantonmcleod-my.sharepoint.com/personal/alex_campbell_pantonmcleod_co_uk/Documents/CodeStuffs/equipment_portal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{65FC2E82-7604-41E0-B33D-F59F96D9306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{162CA050-1AF2-4D2D-A3C9-0C9433AF6953}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{65FC2E82-7604-41E0-B33D-F59F96D9306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76E9B269-DB7A-4D8D-AEF5-805098FBD48E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{3B0124D6-ED40-4854-9E06-1CC63E7C882D}"/>
   </bookViews>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="264">
   <si>
     <t>SAGE REFERENCE</t>
   </si>
@@ -769,30 +769,15 @@
     <t>chemical pumps are fucked</t>
   </si>
   <si>
-    <t>old</t>
-  </si>
-  <si>
     <t>SL26 BZJ</t>
   </si>
   <si>
-    <t>------&gt;</t>
-  </si>
-  <si>
-    <t>joe repairs</t>
-  </si>
-  <si>
     <t>in BFO</t>
   </si>
   <si>
-    <t>BZJ</t>
-  </si>
-  <si>
     <t>SL26 BCO</t>
   </si>
   <si>
-    <t>repairs?? Never seen</t>
-  </si>
-  <si>
     <t>JUST FOUND OUT ABT</t>
   </si>
   <si>
@@ -802,36 +787,15 @@
     <t>GEN049</t>
   </si>
   <si>
-    <t>16447 (GCBDH-1228650)</t>
-  </si>
-  <si>
-    <t>new one davie had last</t>
-  </si>
-  <si>
     <t>SL26 BFO</t>
   </si>
   <si>
     <t>wales maybe</t>
   </si>
   <si>
-    <t>Service overdue</t>
-  </si>
-  <si>
-    <t>N/a</t>
-  </si>
-  <si>
-    <t>In Service</t>
-  </si>
-  <si>
-    <t>Set for service</t>
-  </si>
-  <si>
     <t>SL26 CXF</t>
   </si>
   <si>
-    <t>needs qr</t>
-  </si>
-  <si>
     <t>PUM044</t>
   </si>
   <si>
@@ -913,9 +877,6 @@
     <t>Possibly 240V (no S/N)</t>
   </si>
   <si>
-    <t>selkirk</t>
-  </si>
-  <si>
     <t>PUM112</t>
   </si>
   <si>
@@ -923,6 +884,90 @@
   </si>
   <si>
     <t>stolen</t>
+  </si>
+  <si>
+    <t>SL26 CXG</t>
+  </si>
+  <si>
+    <t>ESU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QR </t>
+  </si>
+  <si>
+    <t>exploded to be scrapped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idk where this is </t>
+  </si>
+  <si>
+    <t>GEN080</t>
+  </si>
+  <si>
+    <t>QR</t>
+  </si>
+  <si>
+    <t>SL26 XZV</t>
+  </si>
+  <si>
+    <t>repairs</t>
+  </si>
+  <si>
+    <t>GEN081</t>
+  </si>
+  <si>
+    <t>GCBGT-2506919 (801749)</t>
+  </si>
+  <si>
+    <t>GEN082</t>
+  </si>
+  <si>
+    <t>GCBDH-1228560 (16447)</t>
+  </si>
+  <si>
+    <t>QR - CXK</t>
+  </si>
+  <si>
+    <t>set for service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set for service </t>
+  </si>
+  <si>
+    <t>QR -CXF</t>
+  </si>
+  <si>
+    <t>PUM080</t>
+  </si>
+  <si>
+    <t>PUM081</t>
+  </si>
+  <si>
+    <t>PUM082</t>
+  </si>
+  <si>
+    <t>set for repair</t>
+  </si>
+  <si>
+    <t>PUM083</t>
+  </si>
+  <si>
+    <t>stoneygate</t>
+  </si>
+  <si>
+    <t>PUM084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stoneygate </t>
+  </si>
+  <si>
+    <t>1x 2" BFO &amp; BCO</t>
+  </si>
+  <si>
+    <t>2x 2" BZJ</t>
+  </si>
+  <si>
+    <t>also had a 440 (small sub)</t>
   </si>
 </sst>
 </file>
@@ -932,7 +977,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -985,8 +1030,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1007,18 +1057,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1243,10 +1311,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1260,7 +1348,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1323,9 +1411,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1353,16 +1438,16 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1377,32 +1462,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1423,52 +1508,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1477,7 +1523,77 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1485,41 +1601,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{84664C61-458C-465E-9F74-3D1CD7A96CE6}"/>
   </cellStyles>
-  <dxfs count="155">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+  <dxfs count="130">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1717,7 +1801,9 @@
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1732,54 +1818,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -1801,6 +1839,7 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -1810,21 +1849,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1838,7 +1863,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1930,9 +1955,7 @@
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
+        <left/>
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
@@ -1949,14 +1972,16 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </right>
-        <top/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
         <vertical/>
         <horizontal/>
@@ -1966,71 +1991,18 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </right>
         <top/>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
@@ -2052,6 +2024,7 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -2061,88 +2034,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -2157,7 +2048,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2359,31 +2250,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
@@ -2422,6 +2288,14 @@
       <fill>
         <patternFill>
           <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2489,98 +2363,12 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2782,7 +2570,438 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2810,374 +3029,6 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3201,6 +3052,76 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3238,95 +3159,99 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E841238-B8AA-42F8-980F-A0F39CF45CE4}" name="Generators" displayName="Generators" ref="A1:L30" totalsRowShown="0" headerRowDxfId="105" dataDxfId="104">
-  <autoFilter ref="A1:L30" xr:uid="{4E841238-B8AA-42F8-980F-A0F39CF45CE4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E841238-B8AA-42F8-980F-A0F39CF45CE4}" name="Generators" displayName="Generators" ref="A1:L31" totalsRowShown="0" headerRowDxfId="127" dataDxfId="60">
+  <autoFilter ref="A1:L31" xr:uid="{4E841238-B8AA-42F8-980F-A0F39CF45CE4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L30">
     <sortCondition ref="A1:A30"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{FBF01029-8468-45F8-8289-F1508C6D786C}" name="SAGE REFERENCE" dataDxfId="103"/>
-    <tableColumn id="2" xr3:uid="{EC225BC8-04F4-4324-B0DE-B4CD46E03F66}" name="Equipment type " dataDxfId="102"/>
-    <tableColumn id="3" xr3:uid="{37107A79-CB14-4F32-9AF9-46348026DEEC}" name="Model " dataDxfId="101"/>
+    <tableColumn id="1" xr3:uid="{FBF01029-8468-45F8-8289-F1508C6D786C}" name="SAGE REFERENCE" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{EC225BC8-04F4-4324-B0DE-B4CD46E03F66}" name="Equipment type " dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{37107A79-CB14-4F32-9AF9-46348026DEEC}" name="Model " dataDxfId="69"/>
     <tableColumn id="4" xr3:uid="{74379293-C2C2-40ED-A7CE-6BC0F776D9A0}" name="Serial Number"/>
-    <tableColumn id="5" xr3:uid="{E4D44111-B1DF-484F-9884-E96DC694E68B}" name="Date into Service" dataDxfId="100"/>
-    <tableColumn id="6" xr3:uid="{BDAFA9A1-B7D9-4D3F-B9F2-37BCAE981C7F}" name="Last Service" dataDxfId="99"/>
-    <tableColumn id="7" xr3:uid="{4B95D808-A111-42A5-93AB-44AA25A09A8E}" name="Next Service" dataDxfId="98"/>
-    <tableColumn id="8" xr3:uid="{0EAA17DF-9A0C-43F3-A5A7-AE7960F67890}" name="Service status" dataDxfId="97"/>
-    <tableColumn id="9" xr3:uid="{E758CE80-AE90-4337-8979-209D9A5D3CF5}" name="Days to next service" dataDxfId="96"/>
-    <tableColumn id="10" xr3:uid="{5F6881B6-5E1F-4282-A48D-BDABFEE16414}" name="Location" dataDxfId="95"/>
-    <tableColumn id="11" xr3:uid="{90463963-07D5-41E4-BF61-BFD7B42D2A8F}" name="Notes" dataDxfId="94"/>
-    <tableColumn id="12" xr3:uid="{C591FF9E-CAEC-4B9E-9E09-27AF2E069563}" name="QR Applied" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{E4D44111-B1DF-484F-9884-E96DC694E68B}" name="Date into Service" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{BDAFA9A1-B7D9-4D3F-B9F2-37BCAE981C7F}" name="Last Service" dataDxfId="67"/>
+    <tableColumn id="7" xr3:uid="{4B95D808-A111-42A5-93AB-44AA25A09A8E}" name="Next Service" dataDxfId="66"/>
+    <tableColumn id="8" xr3:uid="{0EAA17DF-9A0C-43F3-A5A7-AE7960F67890}" name="Service status" dataDxfId="65">
+      <calculatedColumnFormula>IF(G2&lt;TODAY(),"Service overdue","In Service")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{E758CE80-AE90-4337-8979-209D9A5D3CF5}" name="Days to next service" dataDxfId="64">
+      <calculatedColumnFormula>IF((G2-TODAY())&gt;0,(G2-TODAY()),"N/a")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{5F6881B6-5E1F-4282-A48D-BDABFEE16414}" name="Location" dataDxfId="63"/>
+    <tableColumn id="11" xr3:uid="{90463963-07D5-41E4-BF61-BFD7B42D2A8F}" name="Notes" dataDxfId="62"/>
+    <tableColumn id="12" xr3:uid="{C591FF9E-CAEC-4B9E-9E09-27AF2E069563}" name="QR Applied" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{67265275-5EEA-4462-A9DC-E2989E840827}" name="Pumps" displayName="Pumps" ref="A1:L37" totalsRowShown="0" headerRowDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{67265275-5EEA-4462-A9DC-E2989E840827}" name="Pumps" displayName="Pumps" ref="A1:L37" totalsRowShown="0" headerRowDxfId="126">
   <autoFilter ref="A1:L37" xr:uid="{67265275-5EEA-4462-A9DC-E2989E840827}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L37">
     <sortCondition ref="A1:A37"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{1BE48298-1B91-4744-B3D3-BA050AC2ACFD}" name="SAGE REFERENCE" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{4361A13A-1C0E-4041-A030-F8B6A5049A1A}" name="Equipment type " dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{1BE48298-1B91-4744-B3D3-BA050AC2ACFD}" name="SAGE REFERENCE" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{4361A13A-1C0E-4041-A030-F8B6A5049A1A}" name="Equipment type " dataDxfId="43"/>
     <tableColumn id="3" xr3:uid="{1410BC8F-319B-413D-9750-2DF21C5104C5}" name="Model "/>
-    <tableColumn id="4" xr3:uid="{9A33259E-1B32-469E-96CA-0AC38B70E7E1}" name="Serial Number" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{0A0B60EC-CBD9-41EE-B828-D30664154015}" name="Date into Service" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{A1796AD3-051E-44A1-BD78-8586A5CF03F3}" name="Last Service" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{B5B6D5BC-6114-4BBB-B306-294ACAD488AE}" name="Next Service" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{CEC7940B-1955-48EE-B0B2-374E88B1714C}" name="Service status" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{606DAEDD-1E85-49C5-9139-2565DADF64D7}" name="Days to next service" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{CDC6DD74-02CA-4BC2-A2AE-5F3CCEBFCAB7}" name="Location" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{FEC82889-F1E7-4DEA-9649-67DAB0E24C8B}" name="Notes" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{E0E8DE59-8C63-4D3B-8ECF-AE97D0D7841B}" name="QR Applied" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{9A33259E-1B32-469E-96CA-0AC38B70E7E1}" name="Serial Number" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{0A0B60EC-CBD9-41EE-B828-D30664154015}" name="Date into Service" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{A1796AD3-051E-44A1-BD78-8586A5CF03F3}" name="Last Service" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{B5B6D5BC-6114-4BBB-B306-294ACAD488AE}" name="Next Service" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{CEC7940B-1955-48EE-B0B2-374E88B1714C}" name="Service status" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{606DAEDD-1E85-49C5-9139-2565DADF64D7}" name="Days to next service" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{CDC6DD74-02CA-4BC2-A2AE-5F3CCEBFCAB7}" name="Location" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{FEC82889-F1E7-4DEA-9649-67DAB0E24C8B}" name="Notes" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{E0E8DE59-8C63-4D3B-8ECF-AE97D0D7841B}" name="QR Applied" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5264EB1D-0653-4FBA-BE40-AF3278217271}" name="Subs" displayName="Subs" ref="A1:L31" totalsRowShown="0" headerRowDxfId="154">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5264EB1D-0653-4FBA-BE40-AF3278217271}" name="Subs" displayName="Subs" ref="A1:L31" totalsRowShown="0" headerRowDxfId="125">
   <autoFilter ref="A1:L31" xr:uid="{5264EB1D-0653-4FBA-BE40-AF3278217271}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L31">
     <sortCondition ref="A1:A31"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{94F05F34-F349-4181-A542-E52629C9E211}" name="SAGE REFERENCE" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{B2998673-879F-462C-B926-F678E0D52D3C}" name="Equipment type " dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{390F5B0D-42AB-41CD-A60C-1968F68454DF}" name="Model " dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{9DD80FAC-5B50-493A-9407-465B86E399D4}" name="Serial Number" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{40E0B144-4F24-4AED-9991-D68BC84D18F8}" name="Date into Service" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{FE144FC2-5CD5-4A35-BEF7-F5433E635BFA}" name="Last Service" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{E115D80D-1021-419C-8E36-14132EEE8DB3}" name="Next Service" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{B56BBCEC-2EA7-4FC8-8C0F-4867CD1B2D62}" name="Service status" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{EA3C5FC1-1FDD-4A20-B085-615154512CA5}" name="Days to next service" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{91115C14-BB48-43C1-91A7-8EECC8D4C95E}" name="Location" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{CFD7031D-6696-4A9F-B4B4-6C1502D766D0}" name="Notes" dataDxfId="28"/>
-    <tableColumn id="12" xr3:uid="{16D13AE1-A43C-4D23-926B-FFF963A1206D}" name="QR Applied" dataDxfId="153"/>
+    <tableColumn id="1" xr3:uid="{94F05F34-F349-4181-A542-E52629C9E211}" name="SAGE REFERENCE" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{B2998673-879F-462C-B926-F678E0D52D3C}" name="Equipment type " dataDxfId="124"/>
+    <tableColumn id="3" xr3:uid="{390F5B0D-42AB-41CD-A60C-1968F68454DF}" name="Model " dataDxfId="123"/>
+    <tableColumn id="4" xr3:uid="{9DD80FAC-5B50-493A-9407-465B86E399D4}" name="Serial Number" dataDxfId="122"/>
+    <tableColumn id="5" xr3:uid="{40E0B144-4F24-4AED-9991-D68BC84D18F8}" name="Date into Service" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{FE144FC2-5CD5-4A35-BEF7-F5433E635BFA}" name="Last Service" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{E115D80D-1021-419C-8E36-14132EEE8DB3}" name="Next Service" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{B56BBCEC-2EA7-4FC8-8C0F-4867CD1B2D62}" name="Service status" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{EA3C5FC1-1FDD-4A20-B085-615154512CA5}" name="Days to next service" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{91115C14-BB48-43C1-91A7-8EECC8D4C95E}" name="Location" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{CFD7031D-6696-4A9F-B4B4-6C1502D766D0}" name="Notes" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{16D13AE1-A43C-4D23-926B-FFF963A1206D}" name="QR Applied" dataDxfId="121"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3CB46473-0F56-4697-9E05-105E91D7F79C}" name="Dosing" displayName="Dosing" ref="A1:K10" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{3CB46473-0F56-4697-9E05-105E91D7F79C}" name="Dosing" displayName="Dosing" ref="A1:K10" totalsRowShown="0" headerRowDxfId="129" dataDxfId="0" tableBorderDxfId="128">
   <autoFilter ref="A1:K10" xr:uid="{3CB46473-0F56-4697-9E05-105E91D7F79C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K10">
     <sortCondition ref="A1:A10"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{78FBB022-4BB0-4456-A165-7CCF3961FC50}" name="SAGE REFERENCE" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{1357E97B-6CCF-4EDD-A644-D2EFA80150B6}" name="Equipment type " dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{A7FDDD8B-EEE1-4643-BF76-6562F3C57913}" name="Model " dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{17707999-51FA-45D4-89F9-28C44EA09143}" name="Serial Number" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{A621761E-8987-49F7-A3C9-95D450D627CB}" name="Date into Service" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{F77E0786-880E-4E7B-B155-07D0C2AF24EF}" name="Last Service" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{CC5D4B36-C3BE-4201-B836-4DCC3F9050FB}" name="Next Service" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{8B04D38A-1842-408A-904F-30CA73458362}" name="Service status" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{D86BD887-89A0-4456-B6A9-E6800690CAC8}" name="Days to next service" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{5E10A458-67BF-4206-BB92-B826AC314BFD}" name="Location" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{BECA969B-8F29-4B41-8ACC-1560629B4A30}" name="Notes" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{78FBB022-4BB0-4456-A165-7CCF3961FC50}" name="SAGE REFERENCE" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{1357E97B-6CCF-4EDD-A644-D2EFA80150B6}" name="Equipment type " dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{A7FDDD8B-EEE1-4643-BF76-6562F3C57913}" name="Model " dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{17707999-51FA-45D4-89F9-28C44EA09143}" name="Serial Number" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{A621761E-8987-49F7-A3C9-95D450D627CB}" name="Date into Service" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F77E0786-880E-4E7B-B155-07D0C2AF24EF}" name="Last Service" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{CC5D4B36-C3BE-4201-B836-4DCC3F9050FB}" name="Next Service" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{8B04D38A-1842-408A-904F-30CA73458362}" name="Service status" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{D86BD887-89A0-4456-B6A9-E6800690CAC8}" name="Days to next service" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{5E10A458-67BF-4206-BB92-B826AC314BFD}" name="Location" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{BECA969B-8F29-4B41-8ACC-1560629B4A30}" name="Notes" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3649,7 +3574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5432F16-B5F3-44C1-B803-E23F41653FF2}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
@@ -3705,39 +3630,40 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>6083</v>
+      <c r="A2" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>206</v>
+        <v>13</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="9">
-        <v>46127</v>
+        <v>45782</v>
       </c>
       <c r="G2" s="10">
-        <v>46310</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I2" s="7">
-        <v>92</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="7"/>
+        <f>EDATE(F2,6)</f>
+        <v>45966</v>
+      </c>
+      <c r="H2" s="7" t="str">
+        <f t="shared" ref="H2:H31" ca="1" si="0">IF(G2&lt;TODAY(),"Service overdue","In Service")</f>
+        <v>Service overdue</v>
+      </c>
+      <c r="I2" s="7" t="str">
+        <f t="shared" ref="I2:I31" ca="1" si="1">IF((G2-TODAY())&gt;0,(G2-TODAY()),"N/a")</f>
+        <v>N/a</v>
+      </c>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="L2" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -3748,236 +3674,261 @@
         <v>13</v>
       </c>
       <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="56">
+      <c r="E3" s="13">
         <v>42317</v>
       </c>
       <c r="F3" s="9">
         <v>46086</v>
       </c>
       <c r="G3" s="10">
+        <f>EDATE(F3,6)</f>
         <v>46270</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>214</v>
+      <c r="H3" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I3" s="7">
-        <v>52</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="7"/>
+        <v>236</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>237</v>
+      </c>
       <c r="L3" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>73</v>
+      <c r="A4" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="D4" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="8">
-        <v>42801</v>
+        <v>22</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="F4" s="9">
-        <v>46127</v>
+        <v>46268</v>
       </c>
       <c r="G4" s="10">
-        <v>46310</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>214</v>
+        <f>EDATE(F4,6)</f>
+        <v>46449</v>
+      </c>
+      <c r="H4" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I4" s="7">
-        <v>92</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>180</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K4" s="7"/>
-      <c r="L4" s="15" t="b">
+      <c r="L4" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="60" t="s">
-        <v>77</v>
+      <c r="D5" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="E5" s="8">
-        <v>42801</v>
+        <v>44901</v>
       </c>
       <c r="F5" s="9">
-        <v>45748</v>
+        <v>46268</v>
       </c>
       <c r="G5" s="10">
-        <v>46113</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>213</v>
+        <f>EDATE(F5,6)</f>
+        <v>46449</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>180</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>211</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="K5" s="7"/>
       <c r="L5" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>15</v>
+      <c r="D6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="8">
+        <v>44901</v>
       </c>
       <c r="F6" s="9">
-        <v>45782</v>
+        <v>46136</v>
       </c>
       <c r="G6" s="10">
-        <v>45966</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7" t="s">
-        <v>16</v>
-      </c>
+        <f t="shared" ref="G6:G7" si="2">EDATE(F6,6)</f>
+        <v>46319</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="7"/>
       <c r="L6" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>20</v>
+      <c r="A7" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>23</v>
+      <c r="C7" s="7"/>
+      <c r="D7" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="8">
+        <v>44901</v>
       </c>
       <c r="F7" s="9">
-        <v>46090</v>
+        <v>46126</v>
       </c>
       <c r="G7" s="10">
-        <v>46274</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="2"/>
+        <v>46309</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I7" s="7">
-        <v>56</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>40</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>197</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="K7" s="7"/>
       <c r="L7" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="12" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="E8" s="8">
-        <v>44901</v>
+        <v>45425</v>
       </c>
       <c r="F8" s="9">
-        <v>46136</v>
+        <v>46239</v>
       </c>
       <c r="G8" s="10">
-        <v>46319</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>214</v>
+        <f>EDATE(F8,6)</f>
+        <v>46423</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I8" s="7">
-        <v>101</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>154</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="11" t="b">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="L8" s="15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7" t="s">
-        <v>31</v>
+        <v>13</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="E9" s="8">
-        <v>44901</v>
+        <v>45425</v>
       </c>
       <c r="F9" s="9">
-        <v>46126</v>
+        <v>46212</v>
       </c>
       <c r="G9" s="10">
-        <v>46309</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>214</v>
+        <f t="shared" ref="G9:G29" si="3">EDATE(F9,6)</f>
+        <v>46396</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I9" s="7">
-        <v>91</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>127</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="11" t="b">
@@ -3986,32 +3937,37 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7" t="s">
-        <v>26</v>
+        <v>13</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="E10" s="8">
-        <v>44901</v>
+        <v>45425</v>
       </c>
       <c r="F10" s="9">
-        <v>46071</v>
+        <v>46268</v>
       </c>
       <c r="G10" s="10">
-        <v>46252</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46449</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I10" s="7">
-        <v>34</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>180</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="11" t="b">
@@ -4019,109 +3975,120 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="8">
-        <v>45017</v>
-      </c>
-      <c r="F11" s="9">
-        <v>46154</v>
-      </c>
-      <c r="G11" s="10">
-        <v>46338</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I11" s="7">
-        <v>120</v>
-      </c>
-      <c r="J11" s="7" t="s">
+      <c r="A11" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="58">
+        <v>45099</v>
+      </c>
+      <c r="F11" s="59">
+        <v>46079</v>
+      </c>
+      <c r="G11" s="60">
+        <f t="shared" si="3"/>
+        <v>46260</v>
+      </c>
+      <c r="H11" s="56" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I11" s="56" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>N/a</v>
+      </c>
+      <c r="J11" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="K11" s="7"/>
+      <c r="K11" s="61" t="s">
+        <v>239</v>
+      </c>
       <c r="L11" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" s="8">
-        <v>45099</v>
+        <v>45499</v>
       </c>
       <c r="F12" s="9">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="G12" s="10">
-        <v>46260</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46270</v>
+      </c>
+      <c r="H12" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I12" s="7">
-        <v>42</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="L12" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>70</v>
+        <v>41</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="E13" s="8">
-        <v>45372</v>
+        <v>45446</v>
       </c>
       <c r="F13" s="9">
-        <v>46086</v>
+        <v>46134</v>
       </c>
       <c r="G13" s="10">
-        <v>46270</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46317</v>
+      </c>
+      <c r="H13" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I13" s="7">
-        <v>52</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>48</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="11" t="b">
@@ -4130,34 +4097,37 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="E14" s="8">
         <v>45425</v>
       </c>
       <c r="F14" s="9">
-        <v>46048</v>
+        <v>46071</v>
       </c>
       <c r="G14" s="10">
-        <v>46229</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I14" s="7">
-        <v>11</v>
+        <f t="shared" si="3"/>
+        <v>46252</v>
+      </c>
+      <c r="H14" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I14" s="7" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>N/a</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="11" t="b">
@@ -4166,106 +4136,119 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>36</v>
+      <c r="D15" s="16" t="s">
+        <v>51</v>
       </c>
       <c r="E15" s="8">
-        <v>45425</v>
+        <v>45446</v>
       </c>
       <c r="F15" s="9">
-        <v>46212</v>
+        <v>46010</v>
       </c>
       <c r="G15" s="10">
-        <v>46396</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I15" s="7">
-        <v>178</v>
+        <f t="shared" si="3"/>
+        <v>46192</v>
+      </c>
+      <c r="H15" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I15" s="7" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>N/a</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>198</v>
+      </c>
       <c r="L15" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>37</v>
+      <c r="A16" s="62" t="s">
+        <v>241</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>38</v>
+      <c r="D16" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="E16" s="8">
-        <v>45425</v>
+        <v>45292</v>
       </c>
       <c r="F16" s="9">
-        <v>46079</v>
+        <v>46239</v>
       </c>
       <c r="G16" s="10">
-        <v>46260</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46423</v>
+      </c>
+      <c r="H16" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I16" s="7">
-        <v>42</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>154</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="11" t="b">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="L16" s="15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>48</v>
+        <v>33</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="E17" s="8">
-        <v>45425</v>
-      </c>
-      <c r="F17" s="9">
-        <v>46071</v>
+        <v>45689</v>
+      </c>
+      <c r="F17" s="25">
+        <v>46154</v>
       </c>
       <c r="G17" s="10">
-        <v>46252</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46338</v>
+      </c>
+      <c r="H17" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I17" s="7">
-        <v>34</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>69</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>24</v>
+        <v>199</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="11" t="b">
@@ -4274,146 +4257,158 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>46</v>
+        <v>33</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="E18" s="8">
-        <v>45446</v>
+        <v>45689</v>
       </c>
       <c r="F18" s="9">
-        <v>46134</v>
+        <v>45716</v>
       </c>
       <c r="G18" s="10">
-        <v>46317</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I18" s="7">
-        <v>99</v>
+        <f t="shared" si="3"/>
+        <v>45897</v>
+      </c>
+      <c r="H18" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I18" s="7" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>N/a</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15" t="b">
-        <v>1</v>
+        <v>243</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="L18" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>50</v>
+      <c r="A19" s="62" t="s">
+        <v>245</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>51</v>
+      <c r="D19" s="12" t="s">
+        <v>246</v>
       </c>
       <c r="E19" s="8">
-        <v>45446</v>
+        <v>46266</v>
       </c>
       <c r="F19" s="9">
-        <v>46010</v>
+        <v>46239</v>
       </c>
       <c r="G19" s="10">
-        <v>46192</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>213</v>
+        <f t="shared" si="3"/>
+        <v>46423</v>
+      </c>
+      <c r="H19" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
+      </c>
+      <c r="I19" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>154</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>49</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="L19" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>43</v>
+      <c r="A20" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>44</v>
+      <c r="D20" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="E20" s="8">
-        <v>45499</v>
+        <v>45734</v>
       </c>
       <c r="F20" s="9">
-        <v>46086</v>
+        <v>46118</v>
       </c>
       <c r="G20" s="10">
-        <v>46270</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46301</v>
+      </c>
+      <c r="H20" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I20" s="7">
-        <v>52</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>200</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="K20" s="7"/>
       <c r="L20" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>72</v>
+        <v>33</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="E21" s="8">
-        <v>45552</v>
+        <v>45734</v>
       </c>
       <c r="F21" s="9">
-        <v>46086</v>
+        <v>46118</v>
       </c>
       <c r="G21" s="10">
-        <v>46270</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46301</v>
+      </c>
+      <c r="H21" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I21" s="7">
-        <v>52</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>210</v>
+        <v>29</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="11" t="b">
@@ -4421,35 +4416,38 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>67</v>
+      <c r="A22" s="62" t="s">
+        <v>247</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="9">
+        <v>46127</v>
+      </c>
+      <c r="G22" s="10">
+        <f t="shared" si="3"/>
+        <v>46310</v>
+      </c>
+      <c r="H22" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="8">
-        <v>45594</v>
-      </c>
-      <c r="F22" s="9">
-        <v>46212</v>
-      </c>
-      <c r="G22" s="10">
-        <v>46396</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I22" s="7">
-        <v>178</v>
-      </c>
       <c r="J22" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="11" t="b">
@@ -4458,7 +4456,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>65</v>
+        <v>202</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>59</v>
@@ -4467,61 +4465,69 @@
         <v>41</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>66</v>
+        <v>248</v>
       </c>
       <c r="E23" s="8">
-        <v>45674</v>
+        <v>46090</v>
       </c>
       <c r="F23" s="9">
-        <v>46071</v>
+        <v>46156</v>
       </c>
       <c r="G23" s="10">
-        <v>46252</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46340</v>
+      </c>
+      <c r="H23" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I23" s="7">
-        <v>34</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>71</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>249</v>
+      </c>
       <c r="L23" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>60</v>
+        <v>41</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="E24" s="8">
-        <v>45734</v>
+        <v>45860</v>
       </c>
       <c r="F24" s="9">
-        <v>46118</v>
+        <v>46268</v>
       </c>
       <c r="G24" s="10">
-        <v>46301</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46449</v>
+      </c>
+      <c r="H24" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I24" s="7">
-        <v>83</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>180</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="11" t="b">
@@ -4530,34 +4536,37 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="19">
-        <v>45734</v>
+        <v>41</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="8">
+        <v>45674</v>
       </c>
       <c r="F25" s="9">
-        <v>46118</v>
+        <v>46268</v>
       </c>
       <c r="G25" s="10">
-        <v>46301</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46449</v>
+      </c>
+      <c r="H25" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I25" s="7">
-        <v>83</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>180</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>29</v>
+        <v>199</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="11" t="b">
@@ -4566,81 +4575,87 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="57">
-        <v>45689</v>
-      </c>
-      <c r="F26" s="20">
-        <v>46154</v>
+        <v>41</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="8">
+        <v>45594</v>
+      </c>
+      <c r="F26" s="9">
+        <v>46212</v>
       </c>
       <c r="G26" s="10">
-        <v>46338</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46396</v>
+      </c>
+      <c r="H26" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I26" s="7">
-        <v>120</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>127</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="K26" s="7"/>
+        <v>205</v>
+      </c>
+      <c r="K26" s="53"/>
       <c r="L26" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>56</v>
+      <c r="A27" s="17" t="s">
+        <v>69</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="63">
-        <v>45689</v>
+      <c r="D27" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="8">
+        <v>45372</v>
       </c>
       <c r="F27" s="9">
-        <v>45716</v>
+        <v>46086</v>
       </c>
       <c r="G27" s="10">
-        <v>45897</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>213</v>
+        <f t="shared" si="3"/>
+        <v>46270</v>
+      </c>
+      <c r="H27" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>204</v>
+        <v>250</v>
       </c>
       <c r="L27" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>59</v>
@@ -4648,23 +4663,26 @@
       <c r="C28" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" s="8">
-        <v>45860</v>
+      <c r="D28" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="18">
+        <v>45552</v>
       </c>
       <c r="F28" s="9">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="G28" s="10">
-        <v>46252</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>214</v>
+        <f t="shared" si="3"/>
+        <v>46270</v>
+      </c>
+      <c r="H28" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
       </c>
       <c r="I28" s="7">
-        <v>34</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>203</v>
@@ -4676,107 +4694,176 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="64">
+        <v>42801</v>
+      </c>
+      <c r="F29" s="19">
+        <v>46127</v>
+      </c>
+      <c r="G29" s="10">
+        <f t="shared" si="3"/>
+        <v>46310</v>
+      </c>
+      <c r="H29" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
-      <c r="D29" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="E29" s="19">
-        <v>46090</v>
-      </c>
-      <c r="F29" s="9">
-        <v>46156</v>
-      </c>
-      <c r="G29" s="10">
-        <v>46340</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I29" s="7">
-        <v>122</v>
-      </c>
       <c r="J29" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="65">
+        <v>42801</v>
+      </c>
+      <c r="F30" s="9">
+        <v>45748</v>
+      </c>
+      <c r="G30" s="10">
+        <f>EDATE(F30,12)</f>
+        <v>46113</v>
+      </c>
+      <c r="H30" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I30" s="7" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>N/a</v>
+      </c>
+      <c r="J30" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L29" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="E30" s="58">
-        <v>45292</v>
-      </c>
-      <c r="F30" s="9">
-        <v>46055</v>
-      </c>
-      <c r="G30" s="10">
-        <v>46236</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I30" s="7">
-        <v>18</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="K30" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L30" s="11" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" s="8">
+        <v>45017</v>
+      </c>
+      <c r="F31" s="25">
+        <v>46154</v>
+      </c>
+      <c r="G31" s="10">
+        <f>EDATE(F31,6)</f>
+        <v>46338</v>
+      </c>
+      <c r="H31" s="7" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>In Service</v>
+      </c>
+      <c r="I31" s="7">
+        <f t="shared" ca="1" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A30">
-    <cfRule type="containsBlanks" dxfId="152" priority="7">
+  <conditionalFormatting sqref="A1">
+    <cfRule type="containsBlanks" dxfId="120" priority="23">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E30">
-    <cfRule type="containsText" dxfId="151" priority="4" operator="containsText" text="Pre 2020">
+  <conditionalFormatting sqref="E1">
+    <cfRule type="containsText" dxfId="119" priority="20" operator="containsText" text="Pre 2020">
       <formula>NOT(ISERROR(SEARCH("Pre 2020",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G30">
-    <cfRule type="expression" dxfId="150" priority="11">
+  <conditionalFormatting sqref="J1">
+    <cfRule type="containsText" dxfId="114" priority="24" operator="containsText" text="Wales">
+      <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1">
+    <cfRule type="containsText" dxfId="113" priority="21" operator="containsText" text="QR">
+      <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="112" priority="22" operator="containsText" text="Set for service">
+      <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A31">
+    <cfRule type="expression" dxfId="86" priority="1">
+      <formula>AND(VALUE(RIGHT(A2,LEN(A2)-3))&gt;=80,VALUE(RIGHT(A2,LEN(A2)-3))&lt;100)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A31">
+    <cfRule type="containsBlanks" dxfId="85" priority="4">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E31">
+    <cfRule type="containsText" dxfId="84" priority="8" operator="containsText" text="Pre 2020">
+      <formula>NOT(ISERROR(SEARCH("Pre 2020",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G31">
+    <cfRule type="expression" dxfId="83" priority="14">
       <formula>G2&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="12">
+    <cfRule type="expression" dxfId="82" priority="15">
       <formula>G2&gt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H30">
-    <cfRule type="expression" dxfId="148" priority="9">
+  <conditionalFormatting sqref="H2:H31">
+    <cfRule type="expression" dxfId="81" priority="12">
       <formula>G2&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="147" priority="10">
+    <cfRule type="expression" dxfId="80" priority="13">
       <formula>G2&gt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I30">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="I2:I31">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4785,27 +4872,35 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J30">
-    <cfRule type="containsText" dxfId="146" priority="8" operator="containsText" text="Wales">
-      <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
+  <conditionalFormatting sqref="J2:J31">
+    <cfRule type="cellIs" dxfId="79" priority="3" operator="equal">
+      <formula>"NOT KNOWN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K30">
-    <cfRule type="containsText" dxfId="145" priority="5" operator="containsText" text="QR">
-      <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
+  <conditionalFormatting sqref="K2:K31">
+    <cfRule type="containsText" dxfId="78" priority="2" operator="containsText" text="set for repair">
+      <formula>NOT(ISERROR(SEARCH("set for repair",K2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="144" priority="6" operator="containsText" text="Set for service">
-      <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
+    <cfRule type="containsText" dxfId="77" priority="9" operator="containsText" text="QR">
+      <formula>NOT(ISERROR(SEARCH("QR",K2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="76" priority="10" operator="containsText" text="Set for service">
+      <formula>NOT(ISERROR(SEARCH("Set for service",K2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L30">
-    <cfRule type="containsText" dxfId="143" priority="1" operator="containsText" text="FALSE">
+  <conditionalFormatting sqref="J2:J31">
+    <cfRule type="containsText" dxfId="75" priority="11" operator="containsText" text="Wales">
+      <formula>NOT(ISERROR(SEARCH("Wales",J2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L31">
+    <cfRule type="containsText" dxfId="74" priority="5" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="142" priority="2" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="73" priority="6" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="141" priority="3" operator="containsText" text="IDK">
+    <cfRule type="containsText" dxfId="72" priority="7" operator="containsText" text="IDK">
       <formula>NOT(ISERROR(SEARCH("IDK",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4875,626 +4970,685 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="22">
-        <v>2802</v>
-      </c>
-      <c r="B2" s="22" t="s">
+      <c r="A2" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="23">
-        <v>46127</v>
-      </c>
-      <c r="G2" s="24">
-        <v>46310</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I2" s="22">
-        <v>92</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="22"/>
+      <c r="C2" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="22">
+        <v>46139</v>
+      </c>
+      <c r="G2" s="23">
+        <f t="shared" ref="G2:G17" si="0">EDATE(F2,6)</f>
+        <v>46322</v>
+      </c>
+      <c r="H2" s="21" t="str">
+        <f t="shared" ref="H2:H37" ca="1" si="1">IF(G2&lt;TODAY(),"Service overdue","In Service")</f>
+        <v>In Service</v>
+      </c>
+      <c r="I2" s="21">
+        <f t="shared" ref="I2:I37" ca="1" si="2">IF((G2-TODAY())&gt;0,(G2-TODAY()),"N/a")</f>
+        <v>53</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="21"/>
       <c r="L2" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="25">
-        <v>3402</v>
-      </c>
-      <c r="B3" s="25" t="s">
+      <c r="A3" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="24" t="s">
         <v>84</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="26">
-        <v>46118</v>
-      </c>
-      <c r="G3" s="27">
-        <v>46301</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I3" s="25">
+        <v>87</v>
+      </c>
+      <c r="E3" s="25">
+        <v>45017</v>
+      </c>
+      <c r="F3" s="9">
+        <v>46239</v>
+      </c>
+      <c r="G3" s="26">
+        <f t="shared" si="0"/>
+        <v>46423</v>
+      </c>
+      <c r="H3" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I3" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="L3" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="15" t="b">
+      <c r="C4" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="25">
+        <v>44562</v>
+      </c>
+      <c r="F4" s="25">
+        <v>46086</v>
+      </c>
+      <c r="G4" s="23">
+        <f t="shared" si="0"/>
+        <v>46270</v>
+      </c>
+      <c r="H4" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I4" s="21">
+        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="26">
-        <v>46139</v>
-      </c>
-      <c r="G4" s="24">
-        <v>46322</v>
-      </c>
-      <c r="H4" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I4" s="22">
-        <v>104</v>
-      </c>
-      <c r="J4" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="25"/>
+      <c r="J4" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="24" t="s">
+        <v>251</v>
+      </c>
       <c r="L4" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="25" t="s">
+      <c r="A5" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="E5" s="26" t="s">
+      <c r="D5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="25">
+        <v>44999</v>
+      </c>
+      <c r="F5" s="22">
+        <v>46139</v>
+      </c>
+      <c r="G5" s="23">
+        <f t="shared" si="0"/>
+        <v>46322</v>
+      </c>
+      <c r="H5" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I5" s="21">
+        <f t="shared" ca="1" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="K5" s="24"/>
+      <c r="L5" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="25">
+        <v>45426</v>
+      </c>
+      <c r="F6" s="9">
+        <v>46212</v>
+      </c>
+      <c r="G6" s="26">
+        <f t="shared" si="0"/>
+        <v>46396</v>
+      </c>
+      <c r="H6" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I6" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>127</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="K6" s="24"/>
+      <c r="L6" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="25">
+        <v>45292</v>
+      </c>
+      <c r="F7" s="25">
+        <v>46154</v>
+      </c>
+      <c r="G7" s="26">
+        <f t="shared" si="0"/>
+        <v>46338</v>
+      </c>
+      <c r="H7" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I7" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="K7" s="24"/>
+      <c r="L7" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="25">
+        <v>45687</v>
+      </c>
+      <c r="F8" s="9">
+        <v>46268</v>
+      </c>
+      <c r="G8" s="26">
+        <f t="shared" si="0"/>
+        <v>46449</v>
+      </c>
+      <c r="H8" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I8" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="24"/>
+      <c r="L8" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="25">
+        <v>45502</v>
+      </c>
+      <c r="F9" s="9">
+        <v>46239</v>
+      </c>
+      <c r="G9" s="26">
+        <f t="shared" si="0"/>
+        <v>46423</v>
+      </c>
+      <c r="H9" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I9" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="L9" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="25">
+        <v>45860</v>
+      </c>
+      <c r="F10" s="9">
+        <v>46239</v>
+      </c>
+      <c r="G10" s="26">
+        <f t="shared" si="0"/>
+        <v>46423</v>
+      </c>
+      <c r="H10" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I10" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="L10" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="22">
+        <v>46139</v>
+      </c>
+      <c r="G11" s="23">
+        <f t="shared" si="0"/>
+        <v>46322</v>
+      </c>
+      <c r="H11" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I11" s="21">
+        <f t="shared" ca="1" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="24"/>
+      <c r="L11" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="26">
-        <v>46154</v>
-      </c>
-      <c r="G5" s="24">
-        <v>46338</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I5" s="22">
-        <v>120</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="L5" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="30">
+      <c r="F12" s="9">
         <v>46212</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G12" s="26">
+        <f t="shared" si="0"/>
         <v>46396</v>
       </c>
-      <c r="H6" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I6" s="28">
-        <v>178</v>
-      </c>
-      <c r="J6" s="22" t="s">
+      <c r="H12" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I12" s="21">
+        <f t="shared" ca="1" si="2"/>
+        <v>127</v>
+      </c>
+      <c r="J12" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="28"/>
-      <c r="L6" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="26">
-        <v>46048</v>
-      </c>
-      <c r="G7" s="27">
-        <v>46229</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I7" s="25">
-        <v>11</v>
-      </c>
-      <c r="J7" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="25"/>
-      <c r="L7" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="9">
-        <v>46139</v>
-      </c>
-      <c r="G8" s="27">
-        <v>46322</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I8" s="25">
-        <v>104</v>
-      </c>
-      <c r="J8" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="25"/>
-      <c r="L8" s="15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="26">
-        <v>45894</v>
-      </c>
-      <c r="G9" s="27">
-        <v>46078</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="I9" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="L9" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="26">
-        <v>46134</v>
-      </c>
-      <c r="G10" s="27">
-        <v>46317</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I10" s="25">
-        <v>99</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="25"/>
-      <c r="L10" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="26">
-        <v>45736</v>
-      </c>
-      <c r="G11" s="24">
-        <v>45920</v>
-      </c>
-      <c r="H11" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="L11" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="26">
-        <v>46048</v>
-      </c>
-      <c r="G12" s="27">
-        <v>46229</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I12" s="22">
-        <v>11</v>
-      </c>
-      <c r="J12" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="K12" s="25"/>
+      <c r="K12" s="24"/>
       <c r="L12" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="25" t="s">
+      <c r="A13" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="26">
-        <v>44562</v>
-      </c>
-      <c r="F13" s="26">
-        <v>46086</v>
-      </c>
-      <c r="G13" s="24">
-        <v>46270</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I13" s="22">
-        <v>52</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="K13" s="25"/>
+      <c r="D13" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="25">
+        <v>46154</v>
+      </c>
+      <c r="G13" s="23">
+        <f t="shared" si="0"/>
+        <v>46338</v>
+      </c>
+      <c r="H13" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I13" s="21">
+        <f t="shared" ca="1" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>252</v>
+      </c>
       <c r="L13" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="25" t="s">
+      <c r="A14" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="9">
+        <v>46212</v>
+      </c>
+      <c r="G14" s="30">
+        <f t="shared" si="0"/>
+        <v>46396</v>
+      </c>
+      <c r="H14" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I14" s="27">
+        <f t="shared" ca="1" si="2"/>
         <v>127</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" s="26">
-        <v>44743</v>
-      </c>
-      <c r="F14" s="26">
-        <v>46139</v>
-      </c>
-      <c r="G14" s="27">
-        <v>46322</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I14" s="25">
-        <v>104</v>
-      </c>
-      <c r="J14" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="25"/>
+      <c r="J14" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="27"/>
       <c r="L14" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E15" s="26">
-        <v>44743</v>
-      </c>
-      <c r="F15" s="26">
-        <v>46118</v>
-      </c>
-      <c r="G15" s="24">
-        <v>46301</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I15" s="22">
+      <c r="A15" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="J15" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="25"/>
+      <c r="C15" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="9">
+        <v>46239</v>
+      </c>
+      <c r="G15" s="23">
+        <f t="shared" si="0"/>
+        <v>46423</v>
+      </c>
+      <c r="H15" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I15" s="21">
+        <f t="shared" ca="1" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>238</v>
+      </c>
       <c r="L15" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="25" t="s">
+      <c r="A16" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="26">
+      <c r="D16" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="22">
         <v>46139</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="23">
+        <f t="shared" si="0"/>
         <v>46322</v>
       </c>
-      <c r="H16" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I16" s="22">
-        <v>104</v>
-      </c>
-      <c r="J16" s="22" t="s">
+      <c r="H16" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I16" s="21">
+        <f t="shared" ca="1" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="J16" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="25"/>
+      <c r="K16" s="24"/>
       <c r="L16" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="67" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" s="26">
-        <v>44287</v>
-      </c>
-      <c r="F17" s="26">
-        <v>45736</v>
-      </c>
-      <c r="G17" s="24">
-        <v>45920</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>123</v>
-      </c>
+      <c r="C17" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="25">
+        <v>46118</v>
+      </c>
+      <c r="G17" s="23">
+        <f t="shared" si="0"/>
+        <v>46301</v>
+      </c>
+      <c r="H17" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I17" s="21">
+        <f t="shared" ca="1" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" s="24"/>
       <c r="L17" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="9">
+        <v>46239</v>
+      </c>
+      <c r="G18" s="23">
+        <f>EDATE(F18,6)</f>
+        <v>46423</v>
+      </c>
+      <c r="H18" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I18" s="21">
+        <f t="shared" ca="1" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="L18" s="15" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="30">
-        <v>46010</v>
-      </c>
-      <c r="G18" s="24">
-        <v>46192</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="J18" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="L18" s="11" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>83</v>
@@ -5502,62 +5656,66 @@
       <c r="C19" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="69" t="s">
-        <v>109</v>
+      <c r="D19" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="9">
-        <v>46212</v>
-      </c>
-      <c r="G19" s="33">
-        <v>46396</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I19" s="25">
-        <v>178</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>24</v>
+      <c r="F19" s="25">
+        <v>46118</v>
+      </c>
+      <c r="G19" s="32">
+        <f>EDATE(F19,6)</f>
+        <v>46301</v>
+      </c>
+      <c r="H19" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I19" s="27">
+        <f t="shared" ca="1" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>29</v>
       </c>
       <c r="K19" s="7"/>
-      <c r="L19" s="15" t="b">
+      <c r="L19" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>90</v>
+      <c r="A20" s="68" t="s">
+        <v>254</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>84</v>
-      </c>
+      <c r="C20" s="7"/>
       <c r="D20" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="9">
-        <v>44999</v>
-      </c>
-      <c r="F20" s="9">
-        <v>46139</v>
-      </c>
-      <c r="G20" s="33">
-        <v>46322</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="I20" s="25">
-        <v>104</v>
-      </c>
-      <c r="J20" s="22" t="s">
-        <v>210</v>
+        <v>119</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="25">
+        <v>46127</v>
+      </c>
+      <c r="G20" s="32">
+        <f>EDATE(F20,6)</f>
+        <v>46310</v>
+      </c>
+      <c r="H20" s="24" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I20" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>29</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="11" t="b">
@@ -5565,646 +5723,740 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="25" t="s">
+      <c r="A21" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="25">
+        <v>44287</v>
+      </c>
+      <c r="F21" s="25">
+        <v>45736</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" ref="G21:G29" si="3">EDATE(F21,6)</f>
+        <v>45920</v>
+      </c>
+      <c r="H21" s="33" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I21" s="24" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>N/a</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="25">
+        <v>45736</v>
+      </c>
+      <c r="G22" s="23">
+        <f t="shared" si="3"/>
+        <v>45920</v>
+      </c>
+      <c r="H22" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I22" s="24" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>N/a</v>
+      </c>
+      <c r="J22" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="L22" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="26">
-        <v>45017</v>
-      </c>
-      <c r="F21" s="26">
-        <v>46055</v>
-      </c>
-      <c r="G21" s="10">
-        <v>46236</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="I21" s="25">
-        <v>18</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K21" s="25"/>
-      <c r="L21" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="26">
-        <v>46118</v>
-      </c>
-      <c r="G22" s="24">
-        <v>46301</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I22" s="25">
-        <v>83</v>
-      </c>
-      <c r="J22" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" s="25"/>
-      <c r="L22" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" s="26">
-        <v>45292</v>
-      </c>
-      <c r="F23" s="26">
-        <v>46079</v>
-      </c>
-      <c r="G23" s="27">
-        <v>46260</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I23" s="25">
-        <v>42</v>
-      </c>
-      <c r="J23" s="22" t="s">
+      <c r="D23" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="E23" s="25">
+        <v>46073</v>
+      </c>
+      <c r="F23" s="25">
+        <v>46074</v>
+      </c>
+      <c r="G23" s="23">
+        <f t="shared" si="3"/>
+        <v>46255</v>
+      </c>
+      <c r="H23" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I23" s="24" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>N/a</v>
+      </c>
+      <c r="J23" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="K23" s="25"/>
+      <c r="K23" s="24"/>
       <c r="L23" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="26">
-        <v>45426</v>
-      </c>
-      <c r="F24" s="26">
-        <v>46212</v>
-      </c>
-      <c r="G24" s="27">
-        <v>46396</v>
-      </c>
-      <c r="H24" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I24" s="25">
-        <v>178</v>
-      </c>
-      <c r="J24" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="K24" s="25"/>
+      <c r="A24" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="25">
+        <v>46090</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="24" t="s">
+        <v>212</v>
+      </c>
       <c r="L24" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="9">
-        <v>45502</v>
-      </c>
-      <c r="F25" s="9">
-        <v>46055</v>
-      </c>
-      <c r="G25" s="10">
-        <v>46236</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I25" s="25">
-        <v>18</v>
-      </c>
-      <c r="J25" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="K25" s="7"/>
+      <c r="A25" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" s="25">
+        <v>44743</v>
+      </c>
+      <c r="F25" s="22">
+        <v>46139</v>
+      </c>
+      <c r="G25" s="26">
+        <f t="shared" si="3"/>
+        <v>46322</v>
+      </c>
+      <c r="H25" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I25" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="J25" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="24"/>
       <c r="L25" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="28" t="s">
+      <c r="A26" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="25">
+        <v>44743</v>
+      </c>
+      <c r="F26" s="25">
+        <v>46118</v>
+      </c>
+      <c r="G26" s="26">
+        <f t="shared" si="3"/>
+        <v>46301</v>
+      </c>
+      <c r="H26" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I26" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="24"/>
+      <c r="L26" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="69">
+        <v>46048</v>
+      </c>
+      <c r="G27" s="70">
+        <f>EDATE(F27,6)</f>
+        <v>46229</v>
+      </c>
+      <c r="H27" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I27" s="27" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>N/a</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="L27" s="15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="71" t="s">
+        <v>257</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="E26" s="30">
-        <v>45529</v>
-      </c>
-      <c r="F26" s="30">
-        <v>46048</v>
-      </c>
-      <c r="G26" s="31">
-        <v>46229</v>
-      </c>
-      <c r="H26" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I26" s="28">
-        <v>11</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="25" t="s">
+      <c r="D28" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="22">
+        <v>46139</v>
+      </c>
+      <c r="G28" s="26">
+        <f t="shared" si="3"/>
+        <v>46322</v>
+      </c>
+      <c r="H28" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I28" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="J28" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K28" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="L28" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C29" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" s="26">
-        <v>45538</v>
-      </c>
-      <c r="F27" s="26">
-        <v>46118</v>
-      </c>
-      <c r="G27" s="27">
-        <v>46301</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I27" s="25">
-        <v>83</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K27" s="25"/>
-      <c r="L27" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="67" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" s="26">
-        <v>45538</v>
-      </c>
-      <c r="F28" s="26">
-        <v>46091</v>
-      </c>
-      <c r="G28" s="27">
-        <v>46275</v>
-      </c>
-      <c r="H28" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I28" s="25">
-        <v>57</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K28" s="25"/>
-      <c r="L28" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="26">
-        <v>45292</v>
-      </c>
-      <c r="F29" s="26">
-        <v>46154</v>
-      </c>
-      <c r="G29" s="27">
-        <v>46338</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I29" s="25">
-        <v>120</v>
-      </c>
-      <c r="J29" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="K29" s="25"/>
+      <c r="D29" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="9">
+        <v>46239</v>
+      </c>
+      <c r="G29" s="26">
+        <f t="shared" si="3"/>
+        <v>46423</v>
+      </c>
+      <c r="H29" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I29" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="J29" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K29" s="24" t="s">
+        <v>258</v>
+      </c>
       <c r="L29" s="15" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" s="25" t="s">
+      <c r="A30" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="26">
-        <v>45687</v>
-      </c>
-      <c r="F30" s="26">
-        <v>46071</v>
-      </c>
-      <c r="G30" s="27">
-        <v>46252</v>
-      </c>
-      <c r="H30" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I30" s="25">
-        <v>34</v>
-      </c>
-      <c r="J30" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K30" s="25"/>
+      <c r="D30" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="25">
+        <v>46134</v>
+      </c>
+      <c r="G30" s="26">
+        <f>EDATE(F30,6)</f>
+        <v>46317</v>
+      </c>
+      <c r="H30" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I30" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" s="24"/>
       <c r="L30" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="25" t="s">
+      <c r="A31" s="72" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="E31" s="26">
-        <v>45860</v>
-      </c>
-      <c r="F31" s="26">
-        <v>46032</v>
-      </c>
-      <c r="G31" s="27">
-        <v>46213</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="I31" s="25" t="s">
+      <c r="D31" s="72" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="73">
+        <v>45894</v>
+      </c>
+      <c r="G31" s="74">
+        <f>EDATE(F31,6)</f>
+        <v>46078</v>
+      </c>
+      <c r="H31" s="75" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I31" s="72" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>N/a</v>
+      </c>
+      <c r="J31" s="75"/>
+      <c r="K31" s="72" t="s">
         <v>213</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K31" s="25" t="s">
-        <v>215</v>
       </c>
       <c r="L31" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="B32" s="25" t="s">
+      <c r="A32" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="B32" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C32" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="E32" s="26">
-        <v>45999</v>
-      </c>
-      <c r="F32" s="26">
-        <v>46023</v>
-      </c>
-      <c r="G32" s="27">
-        <v>46204</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="I32" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="J32" s="22" t="s">
+      <c r="C32" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="25">
+        <v>45748</v>
+      </c>
+      <c r="G32" s="26">
+        <f>EDATE(F32,12)</f>
+        <v>46113</v>
+      </c>
+      <c r="H32" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I32" s="24" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>N/a</v>
+      </c>
+      <c r="J32" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="L32" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="25">
+        <v>45529</v>
+      </c>
+      <c r="F33" s="9">
+        <v>46239</v>
+      </c>
+      <c r="G33" s="26">
+        <f>EDATE(F33,6)</f>
+        <v>46423</v>
+      </c>
+      <c r="H33" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I33" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>154</v>
+      </c>
+      <c r="J33" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K33" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="L33" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="E34" s="25">
+        <v>45292</v>
+      </c>
+      <c r="F34" s="9">
+        <v>46079</v>
+      </c>
+      <c r="G34" s="26">
+        <f>EDATE(F34,6)</f>
+        <v>46260</v>
+      </c>
+      <c r="H34" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I34" s="24" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>N/a</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" s="24"/>
+      <c r="L34" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="E35" s="25">
+        <v>45538</v>
+      </c>
+      <c r="F35" s="25">
+        <v>46118</v>
+      </c>
+      <c r="G35" s="26">
+        <f>EDATE(F35,6)</f>
+        <v>46301</v>
+      </c>
+      <c r="H35" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I35" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="J35" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="K32" s="25"/>
-      <c r="L32" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="64" t="s">
-        <v>218</v>
-      </c>
-      <c r="B33" s="66" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="66" t="s">
-        <v>219</v>
-      </c>
-      <c r="E33" s="26">
-        <v>46073</v>
-      </c>
-      <c r="F33" s="26">
-        <v>46074</v>
-      </c>
-      <c r="G33" s="27">
-        <v>46255</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I33" s="25">
-        <v>37</v>
-      </c>
-      <c r="J33" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33" s="25"/>
-      <c r="L33" s="15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="E34" s="26">
-        <v>46090</v>
-      </c>
-      <c r="F34" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="G34" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="H34" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="I34" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="J34" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K34" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="L34" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" s="26">
-        <v>46048</v>
-      </c>
-      <c r="G35" s="27">
-        <v>46229</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="I35" s="25">
-        <v>11</v>
-      </c>
-      <c r="J35" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K35" s="25"/>
+      <c r="K35" s="24"/>
       <c r="L35" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25" t="s">
+      <c r="A36" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B36" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="66" t="s">
+      <c r="C36" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="26">
-        <v>46139</v>
-      </c>
-      <c r="G36" s="27">
-        <v>46322</v>
-      </c>
-      <c r="H36" s="65" t="s">
-        <v>214</v>
-      </c>
-      <c r="I36" s="25">
-        <v>104</v>
-      </c>
-      <c r="J36" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="K36" s="25"/>
+      <c r="D36" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E36" s="25">
+        <v>45538</v>
+      </c>
+      <c r="F36" s="25">
+        <v>46091</v>
+      </c>
+      <c r="G36" s="26">
+        <f>EDATE(F36,6)</f>
+        <v>46275</v>
+      </c>
+      <c r="H36" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>In Service</v>
+      </c>
+      <c r="I36" s="24">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J36" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" s="24" t="s">
+        <v>256</v>
+      </c>
       <c r="L36" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="25">
+        <v>45999</v>
+      </c>
+      <c r="F37" s="25">
+        <v>46023</v>
+      </c>
+      <c r="G37" s="26">
+        <f>EDATE(F37,6)</f>
+        <v>46204</v>
+      </c>
+      <c r="H37" s="21" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>Service overdue</v>
+      </c>
+      <c r="I37" s="24" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>N/a</v>
+      </c>
+      <c r="J37" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" s="24"/>
+      <c r="L37" s="11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C37" s="66" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" s="26">
-        <v>45748</v>
-      </c>
-      <c r="G37" s="27">
-        <v>46113</v>
-      </c>
-      <c r="H37" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="I37" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="J37" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="L37" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A37">
-    <cfRule type="containsBlanks" dxfId="140" priority="4">
+  <conditionalFormatting sqref="A1">
+    <cfRule type="containsBlanks" dxfId="108" priority="20">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E37">
-    <cfRule type="containsText" dxfId="139" priority="1" operator="containsText" text="Pre 2020">
+  <conditionalFormatting sqref="E1">
+    <cfRule type="containsText" dxfId="107" priority="17" operator="containsText" text="Pre 2020">
       <formula>NOT(ISERROR(SEARCH("Pre 2020",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J1">
+    <cfRule type="containsText" dxfId="102" priority="21" operator="containsText" text="Wales">
+      <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1">
+    <cfRule type="containsText" dxfId="101" priority="18" operator="containsText" text="QR">
+      <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="100" priority="19" operator="containsText" text="Set for service">
+      <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A37">
+    <cfRule type="expression" dxfId="59" priority="1">
+      <formula>AND(VALUE(RIGHT(A2,LEN(A2)-3))&gt;=80,VALUE(RIGHT(A2,LEN(A2)-3))&lt;100)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A37">
+    <cfRule type="containsBlanks" dxfId="58" priority="4">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E37 F23:F24">
+    <cfRule type="containsText" dxfId="57" priority="8" operator="containsText" text="Pre 2020">
+      <formula>NOT(ISERROR(SEARCH("Pre 2020",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G2:G37">
-    <cfRule type="expression" dxfId="138" priority="16">
+    <cfRule type="expression" dxfId="56" priority="14">
       <formula>G2&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="17">
+    <cfRule type="expression" dxfId="55" priority="15">
       <formula>G2&gt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H37">
-    <cfRule type="expression" dxfId="136" priority="14">
+    <cfRule type="expression" dxfId="54" priority="12">
       <formula>G2&lt;TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="135" priority="15">
+    <cfRule type="expression" dxfId="53" priority="13">
       <formula>G2&gt;TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I37">
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6213,27 +6465,35 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J37">
-    <cfRule type="containsText" dxfId="134" priority="5" operator="containsText" text="Wales">
-      <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
+  <conditionalFormatting sqref="J2:J37">
+    <cfRule type="cellIs" dxfId="52" priority="3" operator="equal">
+      <formula>"NOT KNOWN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K37">
-    <cfRule type="containsText" dxfId="133" priority="2" operator="containsText" text="QR">
-      <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
+  <conditionalFormatting sqref="K2:K37">
+    <cfRule type="containsText" dxfId="51" priority="2" operator="containsText" text="set for repair">
+      <formula>NOT(ISERROR(SEARCH("set for repair",K2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="132" priority="3" operator="containsText" text="Set for service">
-      <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
+    <cfRule type="containsText" dxfId="50" priority="9" operator="containsText" text="QR">
+      <formula>NOT(ISERROR(SEARCH("QR",K2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="49" priority="10" operator="containsText" text="Set for service">
+      <formula>NOT(ISERROR(SEARCH("Set for service",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J37">
+    <cfRule type="containsText" dxfId="48" priority="11" operator="containsText" text="Wales">
+      <formula>NOT(ISERROR(SEARCH("Wales",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L37">
-    <cfRule type="containsText" dxfId="131" priority="6" operator="containsText" text="FALSE">
+    <cfRule type="containsText" dxfId="47" priority="5" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="130" priority="7" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="46" priority="6" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="129" priority="8" operator="containsText" text="IDK">
+    <cfRule type="containsText" dxfId="45" priority="7" operator="containsText" text="IDK">
       <formula>NOT(ISERROR(SEARCH("IDK",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6303,743 +6563,784 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24">
+        <v>134493</v>
+      </c>
+      <c r="E2" s="25">
+        <v>42244</v>
+      </c>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="L2" s="20"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" s="36"/>
+      <c r="D3" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="38">
+        <v>42220</v>
+      </c>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="L3" s="20"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="41"/>
+      <c r="D4" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="43">
+        <v>42128</v>
+      </c>
+      <c r="F4" s="38"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="L4" s="20"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" s="43">
+        <v>43536</v>
+      </c>
+      <c r="F5" s="38"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="L5" s="20"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="43">
+        <v>43536</v>
+      </c>
+      <c r="F6" s="38"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="36"/>
+      <c r="L6" s="20"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="46">
+        <v>44139</v>
+      </c>
+      <c r="F7" s="47"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="L7" s="20"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="E8" s="47">
+        <v>44139</v>
+      </c>
+      <c r="F8" s="47"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="L8" s="20"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45">
+        <v>237350</v>
+      </c>
+      <c r="E9" s="47">
+        <v>44592</v>
+      </c>
+      <c r="F9" s="47"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45">
+        <v>237251</v>
+      </c>
+      <c r="E10" s="47">
+        <v>44592</v>
+      </c>
+      <c r="F10" s="47"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="L10" s="20"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45">
+        <v>237349</v>
+      </c>
+      <c r="E11" s="47">
+        <v>44592</v>
+      </c>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="L11" s="20"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45">
+        <v>237359</v>
+      </c>
+      <c r="E12" s="47">
+        <v>44592</v>
+      </c>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="20"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45">
+        <v>249490</v>
+      </c>
+      <c r="E13" s="47">
+        <v>44999</v>
+      </c>
+      <c r="F13" s="47"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="20"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45">
+        <v>249496</v>
+      </c>
+      <c r="E14" s="47">
+        <v>44999</v>
+      </c>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="20"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45">
+        <v>249506</v>
+      </c>
+      <c r="E15" s="47">
+        <v>45034</v>
+      </c>
+      <c r="F15" s="47"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45">
+        <v>249507</v>
+      </c>
+      <c r="E16" s="47">
+        <v>45034</v>
+      </c>
+      <c r="F16" s="47"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45">
+        <v>249508</v>
+      </c>
+      <c r="E17" s="47">
+        <v>45034</v>
+      </c>
+      <c r="F17" s="47"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45">
+        <v>220456</v>
+      </c>
+      <c r="E18" s="47">
+        <v>45160</v>
+      </c>
+      <c r="F18" s="47"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45">
+        <v>220457</v>
+      </c>
+      <c r="E19" s="47">
+        <v>45160</v>
+      </c>
+      <c r="F19" s="47"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="45"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45">
+        <v>275396</v>
+      </c>
+      <c r="E20" s="47">
+        <v>45300</v>
+      </c>
+      <c r="F20" s="47"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="45"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45">
+        <v>287399</v>
+      </c>
+      <c r="E21" s="47">
+        <v>45447</v>
+      </c>
+      <c r="F21" s="47"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="K21" s="45"/>
+      <c r="L21" s="20"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45">
+        <v>287404</v>
+      </c>
+      <c r="E22" s="47">
+        <v>45447</v>
+      </c>
+      <c r="F22" s="47"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="K22" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45">
+        <v>287419</v>
+      </c>
+      <c r="E23" s="47">
+        <v>45503</v>
+      </c>
+      <c r="F23" s="47"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="K23" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="L23" s="20"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45">
+        <v>287411</v>
+      </c>
+      <c r="E24" s="47">
+        <v>45534</v>
+      </c>
+      <c r="F24" s="47"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="K24" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45">
+        <v>287416</v>
+      </c>
+      <c r="E25" s="47">
+        <v>45534</v>
+      </c>
+      <c r="F25" s="47"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="K25" s="45"/>
+      <c r="L25" s="20"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="E26" s="47">
+        <v>45644</v>
+      </c>
+      <c r="F26" s="47"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="45"/>
+      <c r="L26" s="20"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" s="47">
+        <v>45644</v>
+      </c>
+      <c r="F27" s="47"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="45"/>
+      <c r="L27" s="20"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="45">
+        <v>312593</v>
+      </c>
+      <c r="E28" s="55">
+        <v>45995</v>
+      </c>
+      <c r="F28" s="47"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="45"/>
+      <c r="L28" s="20"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="76" t="s">
+        <v>220</v>
+      </c>
+      <c r="C29" s="77" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25">
-        <v>134493</v>
-      </c>
-      <c r="E2" s="26">
-        <v>42244</v>
-      </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25" t="s">
+      <c r="D29" s="53">
+        <v>3081620484</v>
+      </c>
+      <c r="E29" s="25">
+        <v>46030</v>
+      </c>
+      <c r="F29" s="46"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="20"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="L2" s="21"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="37" t="s">
+      <c r="B30" s="78" t="s">
+        <v>214</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="79"/>
+      <c r="E30" s="25">
+        <v>46072</v>
+      </c>
+      <c r="F30" s="46"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="20"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="E3" s="39">
-        <v>42220</v>
-      </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="L3" s="21"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="E4" s="44">
-        <v>42128</v>
-      </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="45" t="s">
+      <c r="B31" s="78" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="79"/>
+      <c r="E31" s="25">
+        <v>46184</v>
+      </c>
+      <c r="F31" s="46"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="L4" s="21"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="E5" s="44">
-        <v>43536</v>
-      </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="L5" s="21"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="E6" s="44">
-        <v>43536</v>
-      </c>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="37"/>
-      <c r="L6" s="21"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" s="47">
-        <v>44139</v>
-      </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="46" t="s">
-        <v>233</v>
-      </c>
-      <c r="L7" s="21"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="E8" s="48">
-        <v>44139</v>
-      </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="46" t="s">
-        <v>234</v>
-      </c>
-      <c r="L8" s="21"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46">
-        <v>237350</v>
-      </c>
-      <c r="E9" s="48">
-        <v>44592</v>
-      </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="21"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46">
-        <v>237251</v>
-      </c>
-      <c r="E10" s="48">
-        <v>44592</v>
-      </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="21"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46">
-        <v>237349</v>
-      </c>
-      <c r="E11" s="48">
-        <v>44592</v>
-      </c>
-      <c r="F11" s="48"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="46" t="s">
-        <v>235</v>
-      </c>
-      <c r="L11" s="21"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46">
-        <v>237359</v>
-      </c>
-      <c r="E12" s="48">
-        <v>44592</v>
-      </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="21"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46">
-        <v>249490</v>
-      </c>
-      <c r="E13" s="48">
-        <v>44999</v>
-      </c>
-      <c r="F13" s="48"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="21"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46">
-        <v>249496</v>
-      </c>
-      <c r="E14" s="48">
-        <v>44999</v>
-      </c>
-      <c r="F14" s="48"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="21"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46">
-        <v>249506</v>
-      </c>
-      <c r="E15" s="48">
-        <v>45034</v>
-      </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="21"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46">
-        <v>249507</v>
-      </c>
-      <c r="E16" s="48">
-        <v>45034</v>
-      </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="21"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46">
-        <v>249508</v>
-      </c>
-      <c r="E17" s="48">
-        <v>45034</v>
-      </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="21"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46">
-        <v>220456</v>
-      </c>
-      <c r="E18" s="48">
-        <v>45160</v>
-      </c>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="21"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46">
-        <v>220457</v>
-      </c>
-      <c r="E19" s="48">
-        <v>45160</v>
-      </c>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" s="46"/>
-      <c r="L19" s="21"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46">
-        <v>275396</v>
-      </c>
-      <c r="E20" s="48">
-        <v>45300</v>
-      </c>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="46"/>
-      <c r="L20" s="21"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46">
-        <v>287399</v>
-      </c>
-      <c r="E21" s="48">
-        <v>45447</v>
-      </c>
-      <c r="F21" s="48"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="21"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46">
-        <v>287404</v>
-      </c>
-      <c r="E22" s="48">
-        <v>45447</v>
-      </c>
-      <c r="F22" s="48"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="K22" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="L22" s="21"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46">
-        <v>287419</v>
-      </c>
-      <c r="E23" s="48">
-        <v>45503</v>
-      </c>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="21"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46">
-        <v>287411</v>
-      </c>
-      <c r="E24" s="48">
-        <v>45534</v>
-      </c>
-      <c r="F24" s="48"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="K24" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="L24" s="21"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46">
-        <v>287416</v>
-      </c>
-      <c r="E25" s="48">
-        <v>45534</v>
-      </c>
-      <c r="F25" s="48"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="K25" s="46"/>
-      <c r="L25" s="21"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="D26" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="E26" s="48">
-        <v>45644</v>
-      </c>
-      <c r="F26" s="48"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="K26" s="46"/>
-      <c r="L26" s="21"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="B27" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="46" t="s">
-        <v>186</v>
-      </c>
-      <c r="E27" s="48">
-        <v>45644</v>
-      </c>
-      <c r="F27" s="48"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" s="46"/>
-      <c r="L27" s="21"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="C28" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" s="46">
-        <v>312593</v>
-      </c>
-      <c r="E28" s="48">
-        <v>45995</v>
-      </c>
-      <c r="F28" s="48"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="K28" s="46"/>
-      <c r="L28" s="21"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="65" t="s">
-        <v>237</v>
-      </c>
-      <c r="B29" s="70" t="s">
-        <v>232</v>
-      </c>
-      <c r="C29" s="70" t="s">
-        <v>238</v>
-      </c>
-      <c r="D29" s="70">
-        <v>3081620484</v>
-      </c>
-      <c r="E29" s="71">
-        <v>46030</v>
-      </c>
-      <c r="F29" s="71"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="21"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="65" t="s">
-        <v>239</v>
-      </c>
-      <c r="B30" s="70" t="s">
-        <v>226</v>
-      </c>
-      <c r="C30" s="70" t="s">
-        <v>188</v>
-      </c>
-      <c r="D30" s="70"/>
-      <c r="E30" s="71">
-        <v>46072</v>
-      </c>
-      <c r="F30" s="71"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="21"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="B31" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="C31" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="D31" s="46"/>
-      <c r="E31" s="48">
-        <v>46184</v>
-      </c>
-      <c r="F31" s="48"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="46"/>
-      <c r="L31" s="21"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="20"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A31">
-    <cfRule type="containsBlanks" dxfId="128" priority="4">
+  <conditionalFormatting sqref="A1">
+    <cfRule type="containsBlanks" dxfId="96" priority="11">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E31">
-    <cfRule type="containsText" dxfId="127" priority="1" operator="containsText" text="Pre 2020">
+  <conditionalFormatting sqref="E1">
+    <cfRule type="containsText" dxfId="95" priority="8" operator="containsText" text="Pre 2020">
       <formula>NOT(ISERROR(SEARCH("Pre 2020",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J31">
-    <cfRule type="containsText" dxfId="126" priority="5" operator="containsText" text="Wales">
+  <conditionalFormatting sqref="J1">
+    <cfRule type="containsText" dxfId="94" priority="12" operator="containsText" text="Wales">
       <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K2 K4:K28">
-    <cfRule type="containsText" dxfId="125" priority="3" operator="containsText" text="Set for service">
+  <conditionalFormatting sqref="K1">
+    <cfRule type="containsText" dxfId="93" priority="10" operator="containsText" text="Set for service">
       <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K31">
-    <cfRule type="containsText" dxfId="124" priority="2" operator="containsText" text="QR">
+  <conditionalFormatting sqref="K1">
+    <cfRule type="containsText" dxfId="92" priority="9" operator="containsText" text="QR">
       <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A31">
+    <cfRule type="expression" dxfId="33" priority="1">
+      <formula>AND(VALUE(RIGHT(A2,LEN(A2)-3))&gt;=80,VALUE(RIGHT(A2,LEN(A2)-3))&lt;100)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E31">
+    <cfRule type="containsText" dxfId="32" priority="4" operator="containsText" text="Pre 2020">
+      <formula>NOT(ISERROR(SEARCH("Pre 2020",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J31">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
+      <formula>"NOT KNOWN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K31">
+    <cfRule type="containsText" dxfId="30" priority="2" operator="containsText" text="set for repair">
+      <formula>NOT(ISERROR(SEARCH("set for repair",K2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="QR">
+      <formula>NOT(ISERROR(SEARCH("QR",K2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="6" operator="containsText" text="Set for service">
+      <formula>NOT(ISERROR(SEARCH("Set for service",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J31">
+    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="Wales">
+      <formula>NOT(ISERROR(SEARCH("Wales",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7069,7 +7370,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -7104,229 +7405,252 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
-        <v>241</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28" t="s">
+      <c r="A2" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="30">
+      <c r="E2" s="25">
         <v>44480</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>244</v>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27">
         <v>2022337764</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="29">
         <v>44944</v>
       </c>
-      <c r="F3" s="26"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25" t="s">
+      <c r="F3" s="29"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="25"/>
+      <c r="K3" s="27"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24">
+        <v>2024246395</v>
+      </c>
+      <c r="E4" s="25">
+        <v>45553</v>
+      </c>
+      <c r="F4" s="25"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="80"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24">
+        <v>2024246396</v>
+      </c>
+      <c r="E5" s="25">
+        <v>45553</v>
+      </c>
+      <c r="F5" s="25"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="80"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24">
+        <v>2024251614</v>
+      </c>
+      <c r="E6" s="25">
+        <v>45553</v>
+      </c>
+      <c r="F6" s="25"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25">
+      <c r="C7" s="24"/>
+      <c r="D7" s="24">
         <v>2024130073</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E7" s="25">
         <v>45553</v>
       </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25" t="s">
+      <c r="F7" s="25"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="25"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="K7" s="24"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25">
+      <c r="C8" s="24"/>
+      <c r="D8" s="24">
         <v>2024130074</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E8" s="25">
         <v>45553</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25" t="s">
+      <c r="F8" s="25"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="25"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="25" t="s">
+      <c r="K8" s="24"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25">
-        <v>2024246395</v>
-      </c>
-      <c r="E6" s="26">
+      <c r="C9" s="24"/>
+      <c r="D9" s="24">
+        <v>2025342006</v>
+      </c>
+      <c r="E9" s="25">
+        <v>46085</v>
+      </c>
+      <c r="F9" s="25"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="24"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="67"/>
+      <c r="B10" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24">
+        <v>2014255293</v>
+      </c>
+      <c r="E10" s="25">
         <v>45553</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="25"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25">
-        <v>2024246396</v>
-      </c>
-      <c r="E7" s="26">
-        <v>45553</v>
-      </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="25"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25">
-        <v>2024251614</v>
-      </c>
-      <c r="E8" s="26">
-        <v>45553</v>
-      </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
-        <v>246</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35">
-        <v>2025342006</v>
-      </c>
-      <c r="E9" s="55">
-        <v>46085</v>
-      </c>
-      <c r="F9" s="55"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35" t="s">
+      <c r="F10" s="25"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="35"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
-      <c r="B10" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25">
-        <v>2014255293</v>
-      </c>
-      <c r="E10" s="26">
-        <v>45553</v>
-      </c>
-      <c r="F10" s="26"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>248</v>
+      <c r="K10" s="24" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A10">
-    <cfRule type="containsBlanks" dxfId="123" priority="4">
+  <conditionalFormatting sqref="A1">
+    <cfRule type="containsBlanks" dxfId="91" priority="12">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E10">
-    <cfRule type="containsText" dxfId="122" priority="1" operator="containsText" text="Pre 2020">
+  <conditionalFormatting sqref="E1">
+    <cfRule type="containsText" dxfId="90" priority="9" operator="containsText" text="Pre 2020">
       <formula>NOT(ISERROR(SEARCH("Pre 2020",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I9">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="J1">
+    <cfRule type="containsText" dxfId="89" priority="13" operator="containsText" text="Wales">
+      <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1">
+    <cfRule type="containsText" dxfId="88" priority="10" operator="containsText" text="QR">
+      <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="87" priority="11" operator="containsText" text="Set for service">
+      <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A10">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>AND(VALUE(RIGHT(A2,LEN(A2)-3))&gt;=80,VALUE(RIGHT(A2,LEN(A2)-3))&lt;100)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E10">
+    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="Pre 2020">
+      <formula>NOT(ISERROR(SEARCH("Pre 2020",E2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8:I10 I2">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7335,17 +7659,25 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J10">
-    <cfRule type="containsText" dxfId="121" priority="5" operator="containsText" text="Wales">
-      <formula>NOT(ISERROR(SEARCH("Wales",J1)))</formula>
+  <conditionalFormatting sqref="J2:J10">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+      <formula>"NOT KNOWN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K10">
-    <cfRule type="containsText" dxfId="120" priority="2" operator="containsText" text="QR">
-      <formula>NOT(ISERROR(SEARCH("QR",K1)))</formula>
+  <conditionalFormatting sqref="K2:K10">
+    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="set for repair">
+      <formula>NOT(ISERROR(SEARCH("set for repair",K2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="119" priority="3" operator="containsText" text="Set for service">
-      <formula>NOT(ISERROR(SEARCH("Set for service",K1)))</formula>
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="QR">
+      <formula>NOT(ISERROR(SEARCH("QR",K2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="Set for service">
+      <formula>NOT(ISERROR(SEARCH("Set for service",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J10">
+    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="Wales">
+      <formula>NOT(ISERROR(SEARCH("Wales",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
